--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB918FB-3E5A-4F9E-956B-73E0DE17909A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF896BA2-B6F4-4DE2-9769-1B28B57B20C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4899" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4899" uniqueCount="625">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1932,12 +1932,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -1953,16 +1947,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -2517,7 +2520,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="68">
     <dxf>
       <font>
         <b val="0"/>
@@ -2581,6 +2584,13 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -4467,33 +4477,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="66" headerRowBorderDxfId="65" tableBorderDxfId="64" totalsRowBorderDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="22" dataDxfId="21"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="20" dataDxfId="19"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="18" dataDxfId="17"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="16" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="14" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4818,14 +4828,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43746A7-9034-4253-BBC7-A96C5E7ADA0F}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4836,7 +4846,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>182</v>
       </c>
@@ -4847,7 +4857,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>183</v>
       </c>
@@ -4858,7 +4868,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4869,7 +4879,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4881,7 +4891,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4893,7 +4903,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4904,7 +4914,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -4915,7 +4925,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>184</v>
       </c>
@@ -4926,7 +4936,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -4937,7 +4947,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -4948,7 +4958,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4959,7 +4969,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -4970,7 +4980,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>189</v>
       </c>
@@ -4981,7 +4991,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>190</v>
       </c>
@@ -4992,7 +5002,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>191</v>
       </c>
@@ -5003,7 +5013,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -5014,19 +5024,19 @@
         <v>447</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46244.494947106483</v>
+        <v>46249.322274537037</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>455</v>
       </c>
@@ -5037,7 +5047,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>451</v>
       </c>
@@ -5049,7 +5059,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>456</v>
       </c>
@@ -5061,7 +5071,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>181</v>
       </c>
@@ -5072,7 +5082,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -5083,7 +5093,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>199</v>
       </c>
@@ -5094,7 +5104,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -5105,7 +5115,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>443</v>
       </c>
@@ -5116,7 +5126,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>584</v>
       </c>
@@ -5127,7 +5137,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>586</v>
       </c>
@@ -5138,7 +5148,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>588</v>
       </c>
@@ -5149,7 +5159,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
         <v>590</v>
       </c>
@@ -5160,7 +5170,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
         <v>592</v>
       </c>
@@ -5171,7 +5181,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
         <v>594</v>
       </c>
@@ -5182,7 +5192,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
         <v>596</v>
       </c>
@@ -5193,7 +5203,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
         <v>598</v>
       </c>
@@ -5204,7 +5214,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
         <v>600</v>
       </c>
@@ -5215,7 +5225,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>602</v>
       </c>
@@ -5226,7 +5236,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
         <v>604</v>
       </c>
@@ -5237,7 +5247,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>606</v>
       </c>
@@ -5248,7 +5258,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>608</v>
       </c>
@@ -5275,34 +5285,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="47.1640625" customWidth="1"/>
-    <col min="25" max="25" width="9.1640625" customWidth="1"/>
-    <col min="26" max="26" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.09765625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35.59765625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="56.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>385</v>
       </c>
@@ -5385,7 +5395,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -5464,10 +5474,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="38" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="Y2" s="38" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="Z2" s="38" t="s">
         <v>472</v>
@@ -5476,7 +5486,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -5555,10 +5565,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="38" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="Y3" s="38" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>473</v>
@@ -5567,7 +5577,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -5646,10 +5656,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y4" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z4" s="38" t="s">
         <v>377</v>
@@ -5658,7 +5668,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -5737,10 +5747,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="38" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="Y5" s="38" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="Z5" s="38" t="s">
         <v>474</v>
@@ -5749,7 +5759,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -5828,10 +5838,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y6" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z6" s="38" t="s">
         <v>475</v>
@@ -5840,7 +5850,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -5919,10 +5929,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y7" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z7" s="38" t="s">
         <v>476</v>
@@ -5931,7 +5941,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -6010,10 +6020,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y8" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z8" s="38" t="s">
         <v>477</v>
@@ -6022,7 +6032,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -6101,10 +6111,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y9" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z9" s="38" t="s">
         <v>478</v>
@@ -6113,7 +6123,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -6192,10 +6202,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y10" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z10" s="38" t="s">
         <v>479</v>
@@ -6204,7 +6214,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -6283,10 +6293,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y11" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z11" s="38" t="s">
         <v>480</v>
@@ -6295,7 +6305,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -6374,10 +6384,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="38" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="Y12" s="38" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="Z12" s="38" t="s">
         <v>481</v>
@@ -6386,7 +6396,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -6465,10 +6475,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="38" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="Y13" s="38" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="Z13" s="38" t="s">
         <v>482</v>
@@ -6477,7 +6487,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -6556,10 +6566,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="68" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="Y14" s="69" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="Z14" s="38" t="s">
         <v>483</v>
@@ -6568,7 +6578,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -6648,10 +6658,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y15" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z15" s="53" t="s">
         <v>527</v>
@@ -6661,7 +6671,7 @@
         <v>Discipline of Architecture</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -6741,10 +6751,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y16" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z16" s="53" t="s">
         <v>534</v>
@@ -6754,7 +6764,7 @@
         <v>Construction Discipline</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -6834,10 +6844,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y17" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z17" s="53" t="s">
         <v>529</v>
@@ -6847,7 +6857,7 @@
         <v>Engineering Discipline</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -6927,10 +6937,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y18" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z18" s="53" t="s">
         <v>530</v>
@@ -6940,7 +6950,7 @@
         <v>Specialty Discipline</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -7020,10 +7030,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y19" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z19" s="53" t="s">
         <v>531</v>
@@ -7033,7 +7043,7 @@
         <v>Manufacturing Discipline</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -7113,10 +7123,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y20" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z20" s="53" t="s">
         <v>532</v>
@@ -7126,7 +7136,7 @@
         <v>Management Discipline</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -7206,10 +7216,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y21" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z21" s="53" t="s">
         <v>533</v>
@@ -7219,7 +7229,7 @@
         <v>Real Estate Discipline</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -7299,10 +7309,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y22" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z22" s="53" t="s">
         <v>536</v>
@@ -7312,7 +7322,7 @@
         <v>Legislation Discipline</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -7392,10 +7402,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y23" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z23" s="53" t="s">
         <v>537</v>
@@ -7405,7 +7415,7 @@
         <v>Discipline of Surveys and implementation</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -7485,10 +7495,10 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y24" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z24" s="53" t="s">
         <v>535</v>
@@ -7498,7 +7508,7 @@
         <v>Operation Discipline</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -7578,10 +7588,10 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y25" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z25" s="53" t="s">
         <v>540</v>
@@ -7591,7 +7601,7 @@
         <v>Other Disciplines</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -7671,10 +7681,10 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y26" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z26" s="53" t="s">
         <v>528</v>
@@ -7684,7 +7694,7 @@
         <v>Planning Discipline</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -7764,10 +7774,10 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="38" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Y27" s="38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="Z27" s="53" t="s">
         <v>539</v>
@@ -7779,16 +7789,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA27 A2:B27">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7803,13 +7818,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7274B-2192-4DC4-A644-E1AD662613FF}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>408</v>
       </c>
@@ -7874,7 +7889,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="24">
         <v>2</v>
       </c>
@@ -7956,13 +7971,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA41B1A8-F6C2-4E23-9DBE-2B95F8FB901A}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="27">
         <v>1</v>
       </c>
@@ -7973,7 +7988,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -7998,36 +8013,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02829C2B-674F-4380-82F9-2448D015A8F3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:Y178"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.1640625" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" customWidth="1"/>
+    <col min="3" max="3" width="11.796875" customWidth="1"/>
+    <col min="4" max="4" width="9.296875" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.19921875" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.69921875" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.296875" customWidth="1"/>
+    <col min="11" max="11" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.796875" customWidth="1"/>
+    <col min="13" max="13" width="26.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.69921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>194</v>
       </c>
@@ -8104,7 +8119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -8181,7 +8196,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -8258,7 +8273,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -8335,7 +8350,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -8412,7 +8427,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -8489,7 +8504,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -8566,7 +8581,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -8643,7 +8658,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -8720,7 +8735,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -8797,7 +8812,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -8874,7 +8889,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -8951,7 +8966,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -9028,7 +9043,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -9105,7 +9120,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -9182,7 +9197,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -9259,7 +9274,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -9336,7 +9351,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -9413,7 +9428,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -9490,7 +9505,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -9567,7 +9582,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -9644,7 +9659,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -9721,7 +9736,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -9798,7 +9813,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -9875,7 +9890,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -9952,7 +9967,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -10029,7 +10044,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -10106,7 +10121,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -10183,7 +10198,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -10260,7 +10275,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="43">
         <v>30</v>
       </c>
@@ -10337,7 +10352,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="43">
         <v>31</v>
       </c>
@@ -10414,7 +10429,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="43">
         <v>32</v>
       </c>
@@ -10491,7 +10506,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="43">
         <v>33</v>
       </c>
@@ -10568,7 +10583,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="43">
         <v>34</v>
       </c>
@@ -10645,7 +10660,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="43">
         <v>35</v>
       </c>
@@ -10722,7 +10737,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="43">
         <v>36</v>
       </c>
@@ -10799,7 +10814,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="43">
         <v>37</v>
       </c>
@@ -10876,7 +10891,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="43">
         <v>38</v>
       </c>
@@ -10953,7 +10968,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="43">
         <v>39</v>
       </c>
@@ -11030,7 +11045,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="43">
         <v>40</v>
       </c>
@@ -11107,7 +11122,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="43">
         <v>41</v>
       </c>
@@ -11184,7 +11199,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="43">
         <v>42</v>
       </c>
@@ -11261,7 +11276,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="43">
         <v>43</v>
       </c>
@@ -11338,7 +11353,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="43">
         <v>44</v>
       </c>
@@ -11415,7 +11430,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="43">
         <v>45</v>
       </c>
@@ -11492,7 +11507,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="43">
         <v>46</v>
       </c>
@@ -11569,7 +11584,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="43">
         <v>47</v>
       </c>
@@ -11646,7 +11661,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="43">
         <v>48</v>
       </c>
@@ -11723,7 +11738,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="43">
         <v>49</v>
       </c>
@@ -11800,7 +11815,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="43">
         <v>50</v>
       </c>
@@ -11877,7 +11892,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="43">
         <v>51</v>
       </c>
@@ -11954,7 +11969,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="43">
         <v>52</v>
       </c>
@@ -12031,7 +12046,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="43">
         <v>53</v>
       </c>
@@ -12108,7 +12123,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="43">
         <v>54</v>
       </c>
@@ -12185,7 +12200,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="43">
         <v>55</v>
       </c>
@@ -12262,7 +12277,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="43">
         <v>56</v>
       </c>
@@ -12339,7 +12354,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="43">
         <v>57</v>
       </c>
@@ -12416,7 +12431,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="43">
         <v>58</v>
       </c>
@@ -12493,7 +12508,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="43">
         <v>59</v>
       </c>
@@ -12570,7 +12585,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="43">
         <v>60</v>
       </c>
@@ -12647,7 +12662,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="43">
         <v>61</v>
       </c>
@@ -12724,7 +12739,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="43">
         <v>62</v>
       </c>
@@ -12801,7 +12816,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="43">
         <v>63</v>
       </c>
@@ -12878,7 +12893,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="43">
         <v>64</v>
       </c>
@@ -12955,7 +12970,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="43">
         <v>65</v>
       </c>
@@ -13032,7 +13047,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="43">
         <v>66</v>
       </c>
@@ -13109,7 +13124,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="43">
         <v>67</v>
       </c>
@@ -13186,7 +13201,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="43">
         <v>68</v>
       </c>
@@ -13263,7 +13278,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="43">
         <v>69</v>
       </c>
@@ -13340,7 +13355,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="43">
         <v>70</v>
       </c>
@@ -13417,7 +13432,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="43">
         <v>71</v>
       </c>
@@ -13494,7 +13509,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="43">
         <v>72</v>
       </c>
@@ -13571,7 +13586,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="43">
         <v>73</v>
       </c>
@@ -13648,7 +13663,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="43">
         <v>74</v>
       </c>
@@ -13725,7 +13740,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="43">
         <v>75</v>
       </c>
@@ -13802,7 +13817,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="43">
         <v>76</v>
       </c>
@@ -13879,7 +13894,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="43">
         <v>77</v>
       </c>
@@ -13956,7 +13971,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="43">
         <v>78</v>
       </c>
@@ -14033,7 +14048,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="43">
         <v>79</v>
       </c>
@@ -14110,7 +14125,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="43">
         <v>80</v>
       </c>
@@ -14187,7 +14202,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="43">
         <v>81</v>
       </c>
@@ -14264,7 +14279,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="43">
         <v>82</v>
       </c>
@@ -14341,7 +14356,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="43">
         <v>83</v>
       </c>
@@ -14418,7 +14433,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="43">
         <v>84</v>
       </c>
@@ -14495,7 +14510,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="43">
         <v>85</v>
       </c>
@@ -14572,7 +14587,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="43">
         <v>86</v>
       </c>
@@ -14649,7 +14664,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="43">
         <v>87</v>
       </c>
@@ -14726,7 +14741,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="43">
         <v>88</v>
       </c>
@@ -14803,7 +14818,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="43">
         <v>89</v>
       </c>
@@ -14880,7 +14895,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="43">
         <v>90</v>
       </c>
@@ -14957,7 +14972,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="43">
         <v>91</v>
       </c>
@@ -15034,7 +15049,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="43">
         <v>92</v>
       </c>
@@ -15111,7 +15126,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="43">
         <v>93</v>
       </c>
@@ -15188,7 +15203,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="43">
         <v>94</v>
       </c>
@@ -15265,7 +15280,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="43">
         <v>95</v>
       </c>
@@ -15342,7 +15357,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="43">
         <v>96</v>
       </c>
@@ -15419,7 +15434,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="43">
         <v>97</v>
       </c>
@@ -15496,7 +15511,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="43">
         <v>98</v>
       </c>
@@ -15573,7 +15588,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="43">
         <v>99</v>
       </c>
@@ -15650,7 +15665,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="43">
         <v>100</v>
       </c>
@@ -15727,7 +15742,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="43">
         <v>101</v>
       </c>
@@ -15804,7 +15819,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="43">
         <v>102</v>
       </c>
@@ -15881,7 +15896,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="43">
         <v>103</v>
       </c>
@@ -15958,7 +15973,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="43">
         <v>104</v>
       </c>
@@ -16035,7 +16050,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="43">
         <v>105</v>
       </c>
@@ -16112,7 +16127,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="43">
         <v>106</v>
       </c>
@@ -16189,7 +16204,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="43">
         <v>107</v>
       </c>
@@ -16266,7 +16281,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="43">
         <v>108</v>
       </c>
@@ -16343,7 +16358,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="43">
         <v>109</v>
       </c>
@@ -16420,7 +16435,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="43">
         <v>110</v>
       </c>
@@ -16497,7 +16512,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="43">
         <v>111</v>
       </c>
@@ -16574,7 +16589,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="43">
         <v>112</v>
       </c>
@@ -16651,7 +16666,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="43">
         <v>113</v>
       </c>
@@ -16728,7 +16743,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="43">
         <v>114</v>
       </c>
@@ -16805,7 +16820,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="43">
         <v>115</v>
       </c>
@@ -16882,7 +16897,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="43">
         <v>116</v>
       </c>
@@ -16959,7 +16974,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="43">
         <v>117</v>
       </c>
@@ -17036,7 +17051,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="43">
         <v>118</v>
       </c>
@@ -17113,7 +17128,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="43">
         <v>119</v>
       </c>
@@ -17190,7 +17205,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="43">
         <v>120</v>
       </c>
@@ -17267,7 +17282,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="43">
         <v>121</v>
       </c>
@@ -17344,7 +17359,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="43">
         <v>122</v>
       </c>
@@ -17421,7 +17436,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="43">
         <v>123</v>
       </c>
@@ -17498,7 +17513,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="43">
         <v>124</v>
       </c>
@@ -17575,7 +17590,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="43">
         <v>125</v>
       </c>
@@ -17652,7 +17667,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="43">
         <v>126</v>
       </c>
@@ -17729,7 +17744,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="43">
         <v>127</v>
       </c>
@@ -17806,7 +17821,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="43">
         <v>128</v>
       </c>
@@ -17883,7 +17898,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="43">
         <v>129</v>
       </c>
@@ -17960,7 +17975,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="43">
         <v>130</v>
       </c>
@@ -18037,7 +18052,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="43">
         <v>131</v>
       </c>
@@ -18114,7 +18129,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="43">
         <v>132</v>
       </c>
@@ -18191,7 +18206,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="43">
         <v>133</v>
       </c>
@@ -18268,7 +18283,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="43">
         <v>134</v>
       </c>
@@ -18345,7 +18360,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="43">
         <v>135</v>
       </c>
@@ -18422,7 +18437,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="43">
         <v>136</v>
       </c>
@@ -18499,7 +18514,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="43">
         <v>137</v>
       </c>
@@ -18576,7 +18591,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="43">
         <v>138</v>
       </c>
@@ -18653,7 +18668,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="43">
         <v>139</v>
       </c>
@@ -18730,7 +18745,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="43">
         <v>140</v>
       </c>
@@ -18807,7 +18822,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="43">
         <v>141</v>
       </c>
@@ -18884,7 +18899,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="43">
         <v>142</v>
       </c>
@@ -18961,7 +18976,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="43">
         <v>143</v>
       </c>
@@ -19038,7 +19053,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="43">
         <v>144</v>
       </c>
@@ -19115,7 +19130,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="43">
         <v>145</v>
       </c>
@@ -19192,7 +19207,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="43">
         <v>146</v>
       </c>
@@ -19269,7 +19284,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="43">
         <v>147</v>
       </c>
@@ -19346,7 +19361,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="43">
         <v>148</v>
       </c>
@@ -19423,7 +19438,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="43">
         <v>149</v>
       </c>
@@ -19500,7 +19515,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="43">
         <v>150</v>
       </c>
@@ -19577,7 +19592,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="43">
         <v>151</v>
       </c>
@@ -19654,7 +19669,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="43">
         <v>152</v>
       </c>
@@ -19731,7 +19746,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43">
         <v>153</v>
       </c>
@@ -19808,7 +19823,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="43">
         <v>154</v>
       </c>
@@ -19885,7 +19900,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="43">
         <v>155</v>
       </c>
@@ -19962,7 +19977,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="43">
         <v>156</v>
       </c>
@@ -20039,7 +20054,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="43">
         <v>157</v>
       </c>
@@ -20116,7 +20131,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="43">
         <v>158</v>
       </c>
@@ -20193,7 +20208,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="43">
         <v>159</v>
       </c>
@@ -20270,7 +20285,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="43">
         <v>160</v>
       </c>
@@ -20347,7 +20362,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="43">
         <v>161</v>
       </c>
@@ -20424,7 +20439,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="43">
         <v>162</v>
       </c>
@@ -20501,7 +20516,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="43">
         <v>163</v>
       </c>
@@ -20578,7 +20593,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="43">
         <v>164</v>
       </c>
@@ -20655,7 +20670,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="43">
         <v>165</v>
       </c>
@@ -20732,7 +20747,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="43">
         <v>166</v>
       </c>
@@ -20809,7 +20824,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="43">
         <v>167</v>
       </c>
@@ -20886,7 +20901,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="43">
         <v>168</v>
       </c>
@@ -20963,7 +20978,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="43">
         <v>169</v>
       </c>
@@ -21040,7 +21055,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="43">
         <v>170</v>
       </c>
@@ -21117,7 +21132,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="43">
         <v>171</v>
       </c>
@@ -21194,7 +21209,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="43">
         <v>172</v>
       </c>
@@ -21271,7 +21286,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="43">
         <v>173</v>
       </c>
@@ -21348,7 +21363,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="43">
         <v>174</v>
       </c>
@@ -21425,7 +21440,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="43">
         <v>175</v>
       </c>
@@ -21502,7 +21517,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="43">
         <v>176</v>
       </c>
@@ -21579,7 +21594,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="43">
         <v>177</v>
       </c>
@@ -21656,7 +21671,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="43">
         <v>178</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF896BA2-B6F4-4DE2-9769-1B28B57B20C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDD9B1B-66CE-4E91-9EE8-B3B9A2ACA6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4899" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4979" uniqueCount="653">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1966,6 +1966,90 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Discipline of Architecture</t>
+  </si>
+  <si>
+    <t>Construction Discipline</t>
+  </si>
+  <si>
+    <t>Engineering Discipline</t>
+  </si>
+  <si>
+    <t>Specialty Discipline</t>
+  </si>
+  <si>
+    <t>Manufacturing Discipline</t>
+  </si>
+  <si>
+    <t>Management Discipline</t>
+  </si>
+  <si>
+    <t>Real Estate Discipline</t>
+  </si>
+  <si>
+    <t>Legislation Discipline</t>
+  </si>
+  <si>
+    <t>Discipline of Surveys and implementation</t>
+  </si>
+  <si>
+    <t>Operation Discipline</t>
+  </si>
+  <si>
+    <t>Other Disciplines</t>
+  </si>
+  <si>
+    <t>Planning Discipline</t>
+  </si>
+  <si>
+    <t>Restoration Discipline</t>
+  </si>
+  <si>
+    <t>Disciplina de la Arquitectura</t>
+  </si>
+  <si>
+    <t>Disciplina de la construcción</t>
+  </si>
+  <si>
+    <t>Disciplina de la Ingeniería</t>
+  </si>
+  <si>
+    <t>Disciplina de especialidad</t>
+  </si>
+  <si>
+    <t>Disciplina de fabricación</t>
+  </si>
+  <si>
+    <t>Disciplina de gestión</t>
+  </si>
+  <si>
+    <t>Disciplina inmobiliaria</t>
+  </si>
+  <si>
+    <t>Disciplina de la Legislación</t>
+  </si>
+  <si>
+    <t>Disciplina de las encuestas e implementación</t>
+  </si>
+  <si>
+    <t>Operación Disciplina</t>
+  </si>
+  <si>
+    <t>Otras disciplinas</t>
+  </si>
+  <si>
+    <t>Disciplina de planificación</t>
+  </si>
+  <si>
+    <t>Disciplina de la Restauración</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
   </si>
 </sst>
 </file>
@@ -2520,7 +2604,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="69">
     <dxf>
       <font>
         <b val="0"/>
@@ -2577,6 +2661,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -4477,33 +4569,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65" totalsRowBorderDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="68" headerRowBorderDxfId="67" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="16" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4828,14 +4920,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43746A7-9034-4253-BBC7-A96C5E7ADA0F}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4846,7 +4938,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>182</v>
       </c>
@@ -4857,7 +4949,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>183</v>
       </c>
@@ -4868,7 +4960,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4879,7 +4971,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4891,7 +4983,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4903,7 +4995,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4914,7 +5006,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -4925,7 +5017,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>184</v>
       </c>
@@ -4936,7 +5028,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -4947,7 +5039,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -4958,7 +5050,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4969,7 +5061,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -4980,7 +5072,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>189</v>
       </c>
@@ -4991,7 +5083,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>190</v>
       </c>
@@ -5002,7 +5094,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>191</v>
       </c>
@@ -5013,7 +5105,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -5024,19 +5116,19 @@
         <v>447</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46249.322274537037</v>
+        <v>46253.606524537034</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>455</v>
       </c>
@@ -5047,7 +5139,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="39" t="s">
         <v>451</v>
       </c>
@@ -5059,7 +5151,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="39" t="s">
         <v>456</v>
       </c>
@@ -5071,7 +5163,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>181</v>
       </c>
@@ -5082,7 +5174,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -5093,7 +5185,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>199</v>
       </c>
@@ -5104,7 +5196,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -5115,7 +5207,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="39" t="s">
         <v>443</v>
       </c>
@@ -5126,7 +5218,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39" t="s">
         <v>584</v>
       </c>
@@ -5137,7 +5229,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="39" t="s">
         <v>586</v>
       </c>
@@ -5148,7 +5240,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="39" t="s">
         <v>588</v>
       </c>
@@ -5159,7 +5251,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="39" t="s">
         <v>590</v>
       </c>
@@ -5170,7 +5262,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="39" t="s">
         <v>592</v>
       </c>
@@ -5181,7 +5273,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="39" t="s">
         <v>594</v>
       </c>
@@ -5192,7 +5284,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="39" t="s">
         <v>596</v>
       </c>
@@ -5203,7 +5295,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="39" t="s">
         <v>598</v>
       </c>
@@ -5214,7 +5306,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="39" t="s">
         <v>600</v>
       </c>
@@ -5225,7 +5317,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="39" t="s">
         <v>602</v>
       </c>
@@ -5236,7 +5328,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="39" t="s">
         <v>604</v>
       </c>
@@ -5247,7 +5339,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>606</v>
       </c>
@@ -5258,7 +5350,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="39" t="s">
         <v>608</v>
       </c>
@@ -5284,35 +5376,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC27"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.09765625" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3984375" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.8984375" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="35.59765625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="56.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61" customWidth="1"/>
+    <col min="17" max="17" width="65.5" customWidth="1"/>
+    <col min="18" max="18" width="57.33203125" customWidth="1"/>
+    <col min="19" max="19" width="5" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>385</v>
       </c>
@@ -5364,38 +5458,44 @@
       <c r="Q1" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="S1" s="20" t="s">
         <v>429</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="T1" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="U1" s="20" t="s">
         <v>403</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="V1" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="W1" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="W1" s="59" t="s">
+      <c r="X1" s="59" t="s">
         <v>406</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="Y1" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="AA1" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="Z1" s="20" t="s">
+      <c r="AB1" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="AC1" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="AA1" s="37" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -5451,42 +5551,48 @@
       <c r="Q2" s="52" t="s">
         <v>546</v>
       </c>
-      <c r="R2" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S2" s="53" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="55" t="s">
+        <v>547</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T2" s="53" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="53" t="str">
+      <c r="U2" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="52" t="str">
+      <c r="V2" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="38" t="s">
+      <c r="W2" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W2" s="58" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="38" t="s">
+      <c r="Y2" s="38" t="s">
         <v>620</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Z2" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA2" s="38" t="s">
         <v>621</v>
       </c>
-      <c r="Z2" s="38" t="s">
+      <c r="AB2" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC2" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="AA2" s="55" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -5542,42 +5648,48 @@
       <c r="Q3" s="52" t="s">
         <v>549</v>
       </c>
-      <c r="R3" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S3" s="53" t="str">
+      <c r="R3" s="55" t="s">
+        <v>550</v>
+      </c>
+      <c r="S3" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T3" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="53" t="str">
+      <c r="U3" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="52" t="str">
+      <c r="V3" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="38" t="s">
+      <c r="W3" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W3" s="58" t="str">
+      <c r="X3" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="38" t="s">
+      <c r="Y3" s="38" t="s">
         <v>622</v>
       </c>
-      <c r="Y3" s="38" t="s">
+      <c r="Z3" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA3" s="38" t="s">
         <v>623</v>
       </c>
-      <c r="Z3" s="38" t="s">
+      <c r="AB3" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC3" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="AA3" s="55" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -5633,42 +5745,48 @@
       <c r="Q4" s="52" t="s">
         <v>552</v>
       </c>
-      <c r="R4" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S4" s="53" t="str">
+      <c r="R4" s="55" t="s">
+        <v>553</v>
+      </c>
+      <c r="S4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T4" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="53" t="str">
+      <c r="U4" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="52" t="str">
+      <c r="V4" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="38" t="s">
+      <c r="W4" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W4" s="58" t="str">
+      <c r="X4" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="38" t="s">
+      <c r="Y4" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y4" s="38" t="s">
+      <c r="Z4" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA4" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z4" s="38" t="s">
+      <c r="AB4" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC4" s="38" t="s">
         <v>377</v>
       </c>
-      <c r="AA4" s="55" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -5724,42 +5842,48 @@
       <c r="Q5" s="52" t="s">
         <v>555</v>
       </c>
-      <c r="R5" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S5" s="53" t="str">
+      <c r="R5" s="55" t="s">
+        <v>556</v>
+      </c>
+      <c r="S5" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T5" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="53" t="str">
+      <c r="U5" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="52" t="str">
+      <c r="V5" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="38" t="s">
+      <c r="W5" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W5" s="58" t="str">
+      <c r="X5" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="38" t="s">
+      <c r="Y5" s="38" t="s">
         <v>615</v>
       </c>
-      <c r="Y5" s="38" t="s">
+      <c r="Z5" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA5" s="38" t="s">
         <v>616</v>
       </c>
-      <c r="Z5" s="38" t="s">
+      <c r="AB5" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC5" s="38" t="s">
         <v>474</v>
       </c>
-      <c r="AA5" s="55" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -5815,42 +5939,48 @@
       <c r="Q6" s="52" t="s">
         <v>558</v>
       </c>
-      <c r="R6" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S6" s="53" t="str">
+      <c r="R6" s="55" t="s">
+        <v>559</v>
+      </c>
+      <c r="S6" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T6" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="53" t="str">
+      <c r="U6" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="52" t="str">
+      <c r="V6" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="38" t="s">
+      <c r="W6" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W6" s="58" t="str">
+      <c r="X6" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="38" t="s">
+      <c r="Y6" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y6" s="38" t="s">
+      <c r="Z6" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA6" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z6" s="38" t="s">
+      <c r="AB6" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC6" s="38" t="s">
         <v>475</v>
       </c>
-      <c r="AA6" s="55" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -5906,42 +6036,48 @@
       <c r="Q7" s="52" t="s">
         <v>561</v>
       </c>
-      <c r="R7" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S7" s="53" t="str">
+      <c r="R7" s="55" t="s">
+        <v>562</v>
+      </c>
+      <c r="S7" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T7" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="53" t="str">
+      <c r="U7" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="52" t="str">
+      <c r="V7" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="38" t="s">
+      <c r="W7" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W7" s="58" t="str">
+      <c r="X7" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="38" t="s">
-        <v>613</v>
-      </c>
       <c r="Y7" s="38" t="s">
         <v>613</v>
       </c>
       <c r="Z7" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA7" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB7" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC7" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="AA7" s="55" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -5997,42 +6133,48 @@
       <c r="Q8" s="52" t="s">
         <v>564</v>
       </c>
-      <c r="R8" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S8" s="53" t="str">
+      <c r="R8" s="55" t="s">
+        <v>565</v>
+      </c>
+      <c r="S8" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T8" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="53" t="str">
+      <c r="U8" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="52" t="str">
+      <c r="V8" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="38" t="s">
+      <c r="W8" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W8" s="58" t="str">
+      <c r="X8" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="38" t="s">
-        <v>613</v>
-      </c>
       <c r="Y8" s="38" t="s">
         <v>613</v>
       </c>
       <c r="Z8" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA8" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB8" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC8" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="AA8" s="55" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -6088,42 +6230,48 @@
       <c r="Q9" s="52" t="s">
         <v>567</v>
       </c>
-      <c r="R9" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S9" s="53" t="str">
+      <c r="R9" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="S9" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T9" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="53" t="str">
+      <c r="U9" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="52" t="str">
+      <c r="V9" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="38" t="s">
+      <c r="W9" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W9" s="58" t="str">
+      <c r="X9" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="38" t="s">
-        <v>613</v>
-      </c>
       <c r="Y9" s="38" t="s">
         <v>613</v>
       </c>
       <c r="Z9" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA9" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB9" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC9" s="38" t="s">
         <v>478</v>
       </c>
-      <c r="AA9" s="55" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -6179,42 +6327,48 @@
       <c r="Q10" s="52" t="s">
         <v>570</v>
       </c>
-      <c r="R10" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S10" s="53" t="str">
+      <c r="R10" s="55" t="s">
+        <v>571</v>
+      </c>
+      <c r="S10" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T10" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="53" t="str">
+      <c r="U10" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="52" t="str">
+      <c r="V10" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="38" t="s">
+      <c r="W10" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W10" s="58" t="str">
+      <c r="X10" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="38" t="s">
-        <v>613</v>
-      </c>
       <c r="Y10" s="38" t="s">
         <v>613</v>
       </c>
       <c r="Z10" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA10" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB10" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC10" s="38" t="s">
         <v>479</v>
       </c>
-      <c r="AA10" s="55" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -6270,42 +6424,48 @@
       <c r="Q11" s="52" t="s">
         <v>573</v>
       </c>
-      <c r="R11" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S11" s="53" t="str">
+      <c r="R11" s="55" t="s">
+        <v>574</v>
+      </c>
+      <c r="S11" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T11" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="53" t="str">
+      <c r="U11" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="52" t="str">
+      <c r="V11" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="38" t="s">
+      <c r="W11" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W11" s="58" t="str">
+      <c r="X11" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="38" t="s">
-        <v>613</v>
-      </c>
       <c r="Y11" s="38" t="s">
         <v>613</v>
       </c>
       <c r="Z11" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA11" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB11" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC11" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="AA11" s="55" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -6361,42 +6521,48 @@
       <c r="Q12" s="52" t="s">
         <v>576</v>
       </c>
-      <c r="R12" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S12" s="53" t="str">
+      <c r="R12" s="55" t="s">
+        <v>577</v>
+      </c>
+      <c r="S12" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T12" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="53" t="str">
+      <c r="U12" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="52" t="str">
+      <c r="V12" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="38" t="s">
+      <c r="W12" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W12" s="58" t="str">
+      <c r="X12" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="38" t="s">
+      <c r="Y12" s="38" t="s">
         <v>617</v>
       </c>
-      <c r="Y12" s="38" t="s">
+      <c r="Z12" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA12" s="38" t="s">
         <v>624</v>
       </c>
-      <c r="Z12" s="38" t="s">
+      <c r="AB12" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC12" s="38" t="s">
         <v>481</v>
       </c>
-      <c r="AA12" s="55" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -6452,42 +6618,48 @@
       <c r="Q13" s="52" t="s">
         <v>579</v>
       </c>
-      <c r="R13" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S13" s="53" t="str">
+      <c r="R13" s="55" t="s">
+        <v>580</v>
+      </c>
+      <c r="S13" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T13" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="53" t="str">
+      <c r="U13" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="52" t="str">
+      <c r="V13" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="38" t="s">
+      <c r="W13" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W13" s="58" t="str">
+      <c r="X13" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="38" t="s">
+      <c r="Y13" s="38" t="s">
         <v>617</v>
       </c>
-      <c r="Y13" s="38" t="s">
+      <c r="Z13" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA13" s="38" t="s">
         <v>624</v>
       </c>
-      <c r="Z13" s="38" t="s">
+      <c r="AB13" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC13" s="38" t="s">
         <v>482</v>
       </c>
-      <c r="AA13" s="55" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -6543,42 +6715,48 @@
       <c r="Q14" s="52" t="s">
         <v>582</v>
       </c>
-      <c r="R14" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S14" s="53" t="str">
+      <c r="R14" s="55" t="s">
+        <v>583</v>
+      </c>
+      <c r="S14" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T14" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="53" t="str">
+      <c r="U14" s="53" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="52" t="str">
+      <c r="V14" s="52" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="38" t="s">
+      <c r="W14" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W14" s="58" t="str">
+      <c r="X14" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="68" t="s">
+      <c r="Y14" s="68" t="s">
         <v>618</v>
       </c>
-      <c r="Y14" s="69" t="s">
+      <c r="Z14" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA14" s="69" t="s">
         <v>619</v>
       </c>
-      <c r="Z14" s="38" t="s">
+      <c r="AB14" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC14" s="38" t="s">
         <v>483</v>
       </c>
-      <c r="AA14" s="55" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -6631,47 +6809,51 @@
       <c r="P15" s="38" t="s">
         <v>502</v>
       </c>
-      <c r="Q15" s="38" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Disciplina de la Arquitectura</v>
+      <c r="Q15" s="38" t="s">
+        <v>638</v>
       </c>
       <c r="R15" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S15" s="53" t="str">
-        <f t="shared" ref="S15:U17" si="8">SUBSTITUTE(C15, "_", " ")</f>
+        <v>625</v>
+      </c>
+      <c r="S15" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T15" s="53" t="str">
+        <f t="shared" ref="T15:V17" si="8">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="53" t="str">
+      <c r="U15" s="53" t="str">
         <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="52" t="str">
+      <c r="V15" s="52" t="str">
         <f t="shared" si="8"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V15" s="38" t="s">
+      <c r="W15" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W15" s="58" t="str">
-        <f t="shared" ref="W15:W27" si="9">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="58" t="str">
+        <f t="shared" ref="X15:X27" si="9">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
-      <c r="X15" s="38" t="s">
+      <c r="Y15" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y15" s="38" t="s">
+      <c r="Z15" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA15" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z15" s="53" t="s">
+      <c r="AB15" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC15" s="53" t="s">
         <v>527</v>
       </c>
-      <c r="AA15" s="38" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Discipline of Architecture</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -6724,47 +6906,51 @@
       <c r="P16" s="52" t="s">
         <v>503</v>
       </c>
-      <c r="Q16" s="38" t="str">
-        <f t="shared" ref="Q16:Q27" si="10">_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>Disciplina de la construcción</v>
+      <c r="Q16" s="38" t="s">
+        <v>639</v>
       </c>
       <c r="R16" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S16" s="53" t="str">
+        <v>626</v>
+      </c>
+      <c r="S16" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T16" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="53" t="str">
+      <c r="U16" s="53" t="str">
         <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="52" t="str">
+      <c r="V16" s="52" t="str">
         <f t="shared" si="8"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V16" s="38" t="s">
+      <c r="W16" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W16" s="58" t="str">
+      <c r="X16" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="38" t="s">
+      <c r="Y16" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y16" s="38" t="s">
+      <c r="Z16" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA16" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z16" s="53" t="s">
+      <c r="AB16" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC16" s="53" t="s">
         <v>534</v>
       </c>
-      <c r="AA16" s="38" t="str">
-        <f t="shared" ref="AA16:AA27" si="11">_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>Construction Discipline</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -6817,47 +7003,51 @@
       <c r="P17" s="52" t="s">
         <v>504</v>
       </c>
-      <c r="Q17" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Disciplina de la Ingeniería</v>
+      <c r="Q17" s="38" t="s">
+        <v>640</v>
       </c>
       <c r="R17" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S17" s="53" t="str">
+        <v>627</v>
+      </c>
+      <c r="S17" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T17" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="53" t="str">
+      <c r="U17" s="53" t="str">
         <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="52" t="str">
+      <c r="V17" s="52" t="str">
         <f t="shared" si="8"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V17" s="38" t="s">
+      <c r="W17" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W17" s="58" t="str">
+      <c r="X17" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="38" t="s">
+      <c r="Y17" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y17" s="38" t="s">
+      <c r="Z17" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA17" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z17" s="53" t="s">
+      <c r="AB17" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC17" s="53" t="s">
         <v>529</v>
       </c>
-      <c r="AA17" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Engineering Discipline</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -6910,47 +7100,51 @@
       <c r="P18" s="52" t="s">
         <v>505</v>
       </c>
-      <c r="Q18" s="38" t="str">
+      <c r="Q18" s="38" t="s">
+        <v>641</v>
+      </c>
+      <c r="R18" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="S18" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T18" s="53" t="str">
+        <f t="shared" ref="T18:V27" si="10">SUBSTITUTE(C18, "_", " ")</f>
+        <v>Normativos</v>
+      </c>
+      <c r="U18" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina de especialidad</v>
-      </c>
-      <c r="R18" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S18" s="53" t="str">
-        <f t="shared" ref="S18:U27" si="12">SUBSTITUTE(C18, "_", " ")</f>
-        <v>Normativos</v>
-      </c>
-      <c r="T18" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U18" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V18" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V18" s="38" t="s">
+      <c r="W18" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W18" s="58" t="str">
+      <c r="X18" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="38" t="s">
+      <c r="Y18" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y18" s="38" t="s">
+      <c r="Z18" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA18" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z18" s="53" t="s">
+      <c r="AB18" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC18" s="53" t="s">
         <v>530</v>
       </c>
-      <c r="AA18" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Specialty Discipline</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -7003,47 +7197,51 @@
       <c r="P19" s="52" t="s">
         <v>506</v>
       </c>
-      <c r="Q19" s="38" t="str">
+      <c r="Q19" s="38" t="s">
+        <v>642</v>
+      </c>
+      <c r="R19" s="38" t="s">
+        <v>629</v>
+      </c>
+      <c r="S19" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T19" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina de fabricación</v>
-      </c>
-      <c r="R19" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S19" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U19" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U19" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V19" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V19" s="38" t="s">
+      <c r="W19" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W19" s="58" t="str">
+      <c r="X19" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="38" t="s">
+      <c r="Y19" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y19" s="38" t="s">
+      <c r="Z19" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA19" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z19" s="53" t="s">
+      <c r="AB19" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC19" s="53" t="s">
         <v>531</v>
       </c>
-      <c r="AA19" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Manufacturing Discipline</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -7096,47 +7294,51 @@
       <c r="P20" s="52" t="s">
         <v>507</v>
       </c>
-      <c r="Q20" s="38" t="str">
+      <c r="Q20" s="38" t="s">
+        <v>643</v>
+      </c>
+      <c r="R20" s="38" t="s">
+        <v>630</v>
+      </c>
+      <c r="S20" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T20" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina de gestión</v>
-      </c>
-      <c r="R20" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S20" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U20" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U20" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V20" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V20" s="38" t="s">
+      <c r="W20" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W20" s="58" t="str">
+      <c r="X20" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="38" t="s">
+      <c r="Y20" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y20" s="38" t="s">
+      <c r="Z20" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA20" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z20" s="53" t="s">
+      <c r="AB20" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC20" s="53" t="s">
         <v>532</v>
       </c>
-      <c r="AA20" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Management Discipline</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -7189,47 +7391,51 @@
       <c r="P21" s="52" t="s">
         <v>508</v>
       </c>
-      <c r="Q21" s="38" t="str">
+      <c r="Q21" s="38" t="s">
+        <v>644</v>
+      </c>
+      <c r="R21" s="38" t="s">
+        <v>631</v>
+      </c>
+      <c r="S21" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T21" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina inmobiliaria</v>
-      </c>
-      <c r="R21" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S21" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U21" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U21" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V21" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V21" s="38" t="s">
+      <c r="W21" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W21" s="58" t="str">
+      <c r="X21" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="38" t="s">
+      <c r="Y21" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y21" s="38" t="s">
+      <c r="Z21" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA21" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z21" s="53" t="s">
+      <c r="AB21" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC21" s="53" t="s">
         <v>533</v>
       </c>
-      <c r="AA21" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Real Estate Discipline</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -7282,47 +7488,51 @@
       <c r="P22" s="52" t="s">
         <v>509</v>
       </c>
-      <c r="Q22" s="38" t="str">
+      <c r="Q22" s="38" t="s">
+        <v>645</v>
+      </c>
+      <c r="R22" s="38" t="s">
+        <v>632</v>
+      </c>
+      <c r="S22" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T22" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina de la Legislación</v>
-      </c>
-      <c r="R22" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S22" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U22" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U22" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V22" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V22" s="38" t="s">
+      <c r="W22" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W22" s="58" t="str">
+      <c r="X22" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="38" t="s">
+      <c r="Y22" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y22" s="38" t="s">
+      <c r="Z22" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA22" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z22" s="53" t="s">
+      <c r="AB22" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC22" s="53" t="s">
         <v>536</v>
       </c>
-      <c r="AA22" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Legislation Discipline</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -7375,47 +7585,51 @@
       <c r="P23" s="52" t="s">
         <v>538</v>
       </c>
-      <c r="Q23" s="38" t="str">
-        <f>_xlfn.TRANSLATE(P23,"pt","es")</f>
-        <v>Disciplina de las encuestas e implementación</v>
+      <c r="Q23" s="38" t="s">
+        <v>646</v>
       </c>
       <c r="R23" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S23" s="53" t="str">
-        <f t="shared" si="12"/>
+        <v>633</v>
+      </c>
+      <c r="S23" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T23" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T23" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U23" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U23" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V23" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V23" s="38" t="s">
+      <c r="W23" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W23" s="58" t="str">
+      <c r="X23" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="38" t="s">
+      <c r="Y23" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y23" s="38" t="s">
+      <c r="Z23" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA23" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z23" s="53" t="s">
+      <c r="AB23" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC23" s="53" t="s">
         <v>537</v>
       </c>
-      <c r="AA23" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Discipline of Surveys and implementation</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -7468,47 +7682,51 @@
       <c r="P24" s="52" t="s">
         <v>510</v>
       </c>
-      <c r="Q24" s="38" t="str">
+      <c r="Q24" s="38" t="s">
+        <v>647</v>
+      </c>
+      <c r="R24" s="38" t="s">
+        <v>634</v>
+      </c>
+      <c r="S24" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T24" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Operación Disciplina</v>
-      </c>
-      <c r="R24" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S24" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T24" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U24" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U24" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V24" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V24" s="38" t="s">
+      <c r="W24" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W24" s="58" t="str">
+      <c r="X24" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="X24" s="38" t="s">
+      <c r="Y24" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y24" s="38" t="s">
+      <c r="Z24" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA24" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z24" s="53" t="s">
+      <c r="AB24" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC24" s="53" t="s">
         <v>535</v>
       </c>
-      <c r="AA24" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Operation Discipline</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -7561,47 +7779,51 @@
       <c r="P25" s="52" t="s">
         <v>511</v>
       </c>
-      <c r="Q25" s="38" t="str">
+      <c r="Q25" s="38" t="s">
+        <v>648</v>
+      </c>
+      <c r="R25" s="38" t="s">
+        <v>635</v>
+      </c>
+      <c r="S25" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T25" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Otras disciplinas</v>
-      </c>
-      <c r="R25" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S25" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T25" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U25" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U25" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V25" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V25" s="38" t="s">
+      <c r="W25" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W25" s="58" t="str">
+      <c r="X25" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="X25" s="38" t="s">
+      <c r="Y25" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y25" s="38" t="s">
+      <c r="Z25" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA25" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z25" s="53" t="s">
+      <c r="AB25" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC25" s="53" t="s">
         <v>540</v>
       </c>
-      <c r="AA25" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Other Disciplines</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -7654,47 +7876,51 @@
       <c r="P26" s="52" t="s">
         <v>512</v>
       </c>
-      <c r="Q26" s="38" t="str">
+      <c r="Q26" s="38" t="s">
+        <v>649</v>
+      </c>
+      <c r="R26" s="38" t="s">
+        <v>636</v>
+      </c>
+      <c r="S26" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T26" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina de planificación</v>
-      </c>
-      <c r="R26" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S26" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T26" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U26" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U26" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V26" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V26" s="38" t="s">
+      <c r="W26" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W26" s="58" t="str">
+      <c r="X26" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="X26" s="38" t="s">
+      <c r="Y26" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y26" s="38" t="s">
+      <c r="Z26" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA26" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z26" s="53" t="s">
+      <c r="AB26" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC26" s="53" t="s">
         <v>528</v>
       </c>
-      <c r="AA26" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Planning Discipline</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -7747,69 +7973,78 @@
       <c r="P27" s="52" t="s">
         <v>513</v>
       </c>
-      <c r="Q27" s="38" t="str">
+      <c r="Q27" s="38" t="s">
+        <v>650</v>
+      </c>
+      <c r="R27" s="38" t="s">
+        <v>637</v>
+      </c>
+      <c r="S27" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="T27" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Disciplina de la Restauración</v>
-      </c>
-      <c r="R27" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="S27" s="53" t="str">
-        <f t="shared" si="12"/>
         <v>Normativos</v>
       </c>
-      <c r="T27" s="53" t="str">
-        <f t="shared" si="12"/>
+      <c r="U27" s="53" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U27" s="52" t="str">
-        <f t="shared" si="12"/>
+      <c r="V27" s="52" t="str">
+        <f t="shared" si="10"/>
         <v>NBR.Disciplinas</v>
       </c>
-      <c r="V27" s="38" t="s">
+      <c r="W27" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="W27" s="58" t="str">
+      <c r="X27" s="58" t="str">
         <f t="shared" si="9"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="X27" s="38" t="s">
+      <c r="Y27" s="38" t="s">
         <v>613</v>
       </c>
-      <c r="Y27" s="38" t="s">
+      <c r="Z27" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA27" s="38" t="s">
         <v>614</v>
       </c>
-      <c r="Z27" s="53" t="s">
+      <c r="AB27" s="38" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC27" s="53" t="s">
         <v>539</v>
-      </c>
-      <c r="AA27" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v>Restoration Discipline</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA27 A2:B27">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R27">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W1 A28:XFD1048576 AB1:XFD1" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AD1:XFD1 A28:Q1048576 A1:Q1 S28:Y1048576 AA28:AA1048576 AC28:XFD1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7818,13 +8053,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7274B-2192-4DC4-A644-E1AD662613FF}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>408</v>
       </c>
@@ -7889,7 +8124,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="24">
         <v>2</v>
       </c>
@@ -7971,13 +8206,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA41B1A8-F6C2-4E23-9DBE-2B95F8FB901A}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.796875" customWidth="1"/>
+    <col min="2" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="27">
         <v>1</v>
       </c>
@@ -7988,7 +8223,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -8013,36 +8248,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02829C2B-674F-4380-82F9-2448D015A8F3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:Y178"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" customWidth="1"/>
-    <col min="4" max="4" width="9.296875" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.19921875" customWidth="1"/>
-    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.69921875" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.296875" customWidth="1"/>
-    <col min="11" max="11" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.796875" customWidth="1"/>
-    <col min="13" max="13" width="26.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.19921875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.19921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>194</v>
       </c>
@@ -8119,7 +8354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -8196,7 +8431,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -8273,7 +8508,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -8350,7 +8585,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -8427,7 +8662,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -8504,7 +8739,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -8581,7 +8816,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -8658,7 +8893,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -8735,7 +8970,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -8812,7 +9047,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -8889,7 +9124,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -8966,7 +9201,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -9043,7 +9278,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -9120,7 +9355,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -9197,7 +9432,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -9274,7 +9509,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -9351,7 +9586,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -9428,7 +9663,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -9505,7 +9740,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -9582,7 +9817,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -9659,7 +9894,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -9736,7 +9971,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -9813,7 +10048,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -9890,7 +10125,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -9967,7 +10202,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -10044,7 +10279,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -10121,7 +10356,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -10198,7 +10433,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -10275,7 +10510,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43">
         <v>30</v>
       </c>
@@ -10352,7 +10587,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43">
         <v>31</v>
       </c>
@@ -10429,7 +10664,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="43">
         <v>32</v>
       </c>
@@ -10506,7 +10741,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="43">
         <v>33</v>
       </c>
@@ -10583,7 +10818,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43">
         <v>34</v>
       </c>
@@ -10660,7 +10895,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43">
         <v>35</v>
       </c>
@@ -10737,7 +10972,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43">
         <v>36</v>
       </c>
@@ -10814,7 +11049,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="43">
         <v>37</v>
       </c>
@@ -10891,7 +11126,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="43">
         <v>38</v>
       </c>
@@ -10968,7 +11203,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="43">
         <v>39</v>
       </c>
@@ -11045,7 +11280,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="43">
         <v>40</v>
       </c>
@@ -11122,7 +11357,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="43">
         <v>41</v>
       </c>
@@ -11199,7 +11434,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="43">
         <v>42</v>
       </c>
@@ -11276,7 +11511,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="43">
         <v>43</v>
       </c>
@@ -11353,7 +11588,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="43">
         <v>44</v>
       </c>
@@ -11430,7 +11665,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="43">
         <v>45</v>
       </c>
@@ -11507,7 +11742,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="43">
         <v>46</v>
       </c>
@@ -11584,7 +11819,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="43">
         <v>47</v>
       </c>
@@ -11661,7 +11896,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="43">
         <v>48</v>
       </c>
@@ -11738,7 +11973,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="43">
         <v>49</v>
       </c>
@@ -11815,7 +12050,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="43">
         <v>50</v>
       </c>
@@ -11892,7 +12127,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="43">
         <v>51</v>
       </c>
@@ -11969,7 +12204,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="43">
         <v>52</v>
       </c>
@@ -12046,7 +12281,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="43">
         <v>53</v>
       </c>
@@ -12123,7 +12358,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="43">
         <v>54</v>
       </c>
@@ -12200,7 +12435,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="43">
         <v>55</v>
       </c>
@@ -12277,7 +12512,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="43">
         <v>56</v>
       </c>
@@ -12354,7 +12589,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="43">
         <v>57</v>
       </c>
@@ -12431,7 +12666,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="43">
         <v>58</v>
       </c>
@@ -12508,7 +12743,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="43">
         <v>59</v>
       </c>
@@ -12585,7 +12820,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="43">
         <v>60</v>
       </c>
@@ -12662,7 +12897,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="43">
         <v>61</v>
       </c>
@@ -12739,7 +12974,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="43">
         <v>62</v>
       </c>
@@ -12816,7 +13051,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="43">
         <v>63</v>
       </c>
@@ -12893,7 +13128,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="43">
         <v>64</v>
       </c>
@@ -12970,7 +13205,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43">
         <v>65</v>
       </c>
@@ -13047,7 +13282,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="43">
         <v>66</v>
       </c>
@@ -13124,7 +13359,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="43">
         <v>67</v>
       </c>
@@ -13201,7 +13436,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="43">
         <v>68</v>
       </c>
@@ -13278,7 +13513,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="43">
         <v>69</v>
       </c>
@@ -13355,7 +13590,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="43">
         <v>70</v>
       </c>
@@ -13432,7 +13667,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="43">
         <v>71</v>
       </c>
@@ -13509,7 +13744,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="43">
         <v>72</v>
       </c>
@@ -13586,7 +13821,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="43">
         <v>73</v>
       </c>
@@ -13663,7 +13898,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="43">
         <v>74</v>
       </c>
@@ -13740,7 +13975,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="43">
         <v>75</v>
       </c>
@@ -13817,7 +14052,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="43">
         <v>76</v>
       </c>
@@ -13894,7 +14129,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="43">
         <v>77</v>
       </c>
@@ -13971,7 +14206,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="43">
         <v>78</v>
       </c>
@@ -14048,7 +14283,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="43">
         <v>79</v>
       </c>
@@ -14125,7 +14360,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="43">
         <v>80</v>
       </c>
@@ -14202,7 +14437,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="43">
         <v>81</v>
       </c>
@@ -14279,7 +14514,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="43">
         <v>82</v>
       </c>
@@ -14356,7 +14591,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="43">
         <v>83</v>
       </c>
@@ -14433,7 +14668,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="43">
         <v>84</v>
       </c>
@@ -14510,7 +14745,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="43">
         <v>85</v>
       </c>
@@ -14587,7 +14822,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="43">
         <v>86</v>
       </c>
@@ -14664,7 +14899,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="43">
         <v>87</v>
       </c>
@@ -14741,7 +14976,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="43">
         <v>88</v>
       </c>
@@ -14818,7 +15053,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="43">
         <v>89</v>
       </c>
@@ -14895,7 +15130,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="43">
         <v>90</v>
       </c>
@@ -14972,7 +15207,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="43">
         <v>91</v>
       </c>
@@ -15049,7 +15284,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="43">
         <v>92</v>
       </c>
@@ -15126,7 +15361,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="43">
         <v>93</v>
       </c>
@@ -15203,7 +15438,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="43">
         <v>94</v>
       </c>
@@ -15280,7 +15515,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="43">
         <v>95</v>
       </c>
@@ -15357,7 +15592,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="43">
         <v>96</v>
       </c>
@@ -15434,7 +15669,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="43">
         <v>97</v>
       </c>
@@ -15511,7 +15746,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="43">
         <v>98</v>
       </c>
@@ -15588,7 +15823,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="43">
         <v>99</v>
       </c>
@@ -15665,7 +15900,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="43">
         <v>100</v>
       </c>
@@ -15742,7 +15977,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="43">
         <v>101</v>
       </c>
@@ -15819,7 +16054,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="43">
         <v>102</v>
       </c>
@@ -15896,7 +16131,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="43">
         <v>103</v>
       </c>
@@ -15973,7 +16208,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="43">
         <v>104</v>
       </c>
@@ -16050,7 +16285,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="43">
         <v>105</v>
       </c>
@@ -16127,7 +16362,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="43">
         <v>106</v>
       </c>
@@ -16204,7 +16439,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="43">
         <v>107</v>
       </c>
@@ -16281,7 +16516,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="43">
         <v>108</v>
       </c>
@@ -16358,7 +16593,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="43">
         <v>109</v>
       </c>
@@ -16435,7 +16670,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="43">
         <v>110</v>
       </c>
@@ -16512,7 +16747,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="43">
         <v>111</v>
       </c>
@@ -16589,7 +16824,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="43">
         <v>112</v>
       </c>
@@ -16666,7 +16901,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="43">
         <v>113</v>
       </c>
@@ -16743,7 +16978,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="43">
         <v>114</v>
       </c>
@@ -16820,7 +17055,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="43">
         <v>115</v>
       </c>
@@ -16897,7 +17132,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="43">
         <v>116</v>
       </c>
@@ -16974,7 +17209,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="43">
         <v>117</v>
       </c>
@@ -17051,7 +17286,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="43">
         <v>118</v>
       </c>
@@ -17128,7 +17363,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="43">
         <v>119</v>
       </c>
@@ -17205,7 +17440,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="43">
         <v>120</v>
       </c>
@@ -17282,7 +17517,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="43">
         <v>121</v>
       </c>
@@ -17359,7 +17594,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="43">
         <v>122</v>
       </c>
@@ -17436,7 +17671,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="43">
         <v>123</v>
       </c>
@@ -17513,7 +17748,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="43">
         <v>124</v>
       </c>
@@ -17590,7 +17825,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="43">
         <v>125</v>
       </c>
@@ -17667,7 +17902,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="43">
         <v>126</v>
       </c>
@@ -17744,7 +17979,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="43">
         <v>127</v>
       </c>
@@ -17821,7 +18056,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="43">
         <v>128</v>
       </c>
@@ -17898,7 +18133,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="43">
         <v>129</v>
       </c>
@@ -17975,7 +18210,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="43">
         <v>130</v>
       </c>
@@ -18052,7 +18287,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="43">
         <v>131</v>
       </c>
@@ -18129,7 +18364,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="43">
         <v>132</v>
       </c>
@@ -18206,7 +18441,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="43">
         <v>133</v>
       </c>
@@ -18283,7 +18518,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="43">
         <v>134</v>
       </c>
@@ -18360,7 +18595,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="43">
         <v>135</v>
       </c>
@@ -18437,7 +18672,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="43">
         <v>136</v>
       </c>
@@ -18514,7 +18749,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="43">
         <v>137</v>
       </c>
@@ -18591,7 +18826,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="43">
         <v>138</v>
       </c>
@@ -18668,7 +18903,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="43">
         <v>139</v>
       </c>
@@ -18745,7 +18980,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="43">
         <v>140</v>
       </c>
@@ -18822,7 +19057,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="43">
         <v>141</v>
       </c>
@@ -18899,7 +19134,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="43">
         <v>142</v>
       </c>
@@ -18976,7 +19211,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="43">
         <v>143</v>
       </c>
@@ -19053,7 +19288,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="43">
         <v>144</v>
       </c>
@@ -19130,7 +19365,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="43">
         <v>145</v>
       </c>
@@ -19207,7 +19442,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="43">
         <v>146</v>
       </c>
@@ -19284,7 +19519,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="43">
         <v>147</v>
       </c>
@@ -19361,7 +19596,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="43">
         <v>148</v>
       </c>
@@ -19438,7 +19673,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="43">
         <v>149</v>
       </c>
@@ -19515,7 +19750,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="43">
         <v>150</v>
       </c>
@@ -19592,7 +19827,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="43">
         <v>151</v>
       </c>
@@ -19669,7 +19904,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="43">
         <v>152</v>
       </c>
@@ -19746,7 +19981,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="43">
         <v>153</v>
       </c>
@@ -19823,7 +20058,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="43">
         <v>154</v>
       </c>
@@ -19900,7 +20135,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="43">
         <v>155</v>
       </c>
@@ -19977,7 +20212,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="43">
         <v>156</v>
       </c>
@@ -20054,7 +20289,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="43">
         <v>157</v>
       </c>
@@ -20131,7 +20366,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="43">
         <v>158</v>
       </c>
@@ -20208,7 +20443,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="43">
         <v>159</v>
       </c>
@@ -20285,7 +20520,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="43">
         <v>160</v>
       </c>
@@ -20362,7 +20597,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="43">
         <v>161</v>
       </c>
@@ -20439,7 +20674,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="43">
         <v>162</v>
       </c>
@@ -20516,7 +20751,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="43">
         <v>163</v>
       </c>
@@ -20593,7 +20828,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="43">
         <v>164</v>
       </c>
@@ -20670,7 +20905,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="43">
         <v>165</v>
       </c>
@@ -20747,7 +20982,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="43">
         <v>166</v>
       </c>
@@ -20824,7 +21059,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="43">
         <v>167</v>
       </c>
@@ -20901,7 +21136,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="43">
         <v>168</v>
       </c>
@@ -20978,7 +21213,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="43">
         <v>169</v>
       </c>
@@ -21055,7 +21290,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="43">
         <v>170</v>
       </c>
@@ -21132,7 +21367,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="43">
         <v>171</v>
       </c>
@@ -21209,7 +21444,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="43">
         <v>172</v>
       </c>
@@ -21286,7 +21521,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="43">
         <v>173</v>
       </c>
@@ -21363,7 +21598,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="43">
         <v>174</v>
       </c>
@@ -21440,7 +21675,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="43">
         <v>175</v>
       </c>
@@ -21517,7 +21752,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="43">
         <v>176</v>
       </c>
@@ -21594,7 +21829,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="43">
         <v>177</v>
       </c>
@@ -21671,7 +21906,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="43">
         <v>178</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6095076-C8AB-4FCE-B093-B8D99D60A458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0384939-9754-4163-B790-9F5B02DC90C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6583" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6578" uniqueCount="683">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2124,19 +2124,22 @@
     <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
   </si>
   <si>
-    <t>é.rvt.ambiente</t>
-  </si>
-  <si>
-    <t>é.rvt.andar</t>
-  </si>
-  <si>
-    <t>é.rvt.elemento</t>
-  </si>
-  <si>
-    <t>é.rvt.tipo</t>
-  </si>
-  <si>
-    <t>é.rvt.material</t>
+    <t>é.selecionado.por</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
+  </si>
+  <si>
+    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
+  </si>
+  <si>
+    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
   </si>
 </sst>
 </file>
@@ -2258,7 +2261,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2425,6 +2428,18 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -2704,16 +2719,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2728,13 +2737,19 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="99">
+  <dxfs count="102">
     <dxf>
       <font>
         <b val="0"/>
@@ -2756,15 +2771,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -2796,7 +2803,15 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2812,7 +2827,31 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3063,14 +3102,28 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3187,14 +3240,28 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3311,14 +3378,28 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3435,14 +3516,28 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5313,41 +5408,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:AG183" headerRowCount="0" totalsRowShown="0" headerRowDxfId="98" headerRowBorderDxfId="97" tableBorderDxfId="96" totalsRowBorderDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:AG183" headerRowCount="0" totalsRowShown="0" headerRowDxfId="101" headerRowBorderDxfId="100" tableBorderDxfId="99" totalsRowBorderDxfId="98">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="94" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="92" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="90" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="88" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="86" dataDxfId="85"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="84" dataDxfId="83"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="82" dataDxfId="81"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="80" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="78" dataDxfId="77"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="76" dataDxfId="75"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="26" xr3:uid="{364EAD9F-B4D7-43DB-A456-E20A3CB3829E}" name="Coluna21" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="27" xr3:uid="{0295ED4C-EACC-4AE2-9685-0BAC96EB0ECA}" name="Coluna22" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="28" xr3:uid="{FA29F4FB-AC77-4D38-9885-60A710F77062}" name="Coluna23" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="29" xr3:uid="{A7FAABAE-4A27-4FF5-B0DD-8D1252FAF81E}" name="Coluna24" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="30" xr3:uid="{D98E6886-A8CD-454E-A6E0-0CFCFBAAA7E8}" name="Coluna25" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="31" xr3:uid="{45B42935-10EC-4D9E-8FE5-A6973C46330A}" name="Coluna26" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="32" xr3:uid="{BAA53309-A49A-4131-A521-AABC6126A49F}" name="Coluna27" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="33" xr3:uid="{D12E34CA-3D33-4D44-A383-CFF16E015D81}" name="Coluna28" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="97" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="93" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="91" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="26" xr3:uid="{364EAD9F-B4D7-43DB-A456-E20A3CB3829E}" name="Coluna21" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="27" xr3:uid="{0295ED4C-EACC-4AE2-9685-0BAC96EB0ECA}" name="Coluna22" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="28" xr3:uid="{FA29F4FB-AC77-4D38-9885-60A710F77062}" name="Coluna23" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="29" xr3:uid="{A7FAABAE-4A27-4FF5-B0DD-8D1252FAF81E}" name="Coluna24" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="30" xr3:uid="{D98E6886-A8CD-454E-A6E0-0CFCFBAAA7E8}" name="Coluna25" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="31" xr3:uid="{45B42935-10EC-4D9E-8FE5-A6973C46330A}" name="Coluna26" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="32" xr3:uid="{BAA53309-A49A-4131-A521-AABC6126A49F}" name="Coluna27" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="33" xr3:uid="{D12E34CA-3D33-4D44-A383-CFF16E015D81}" name="Coluna28" headerRowDxfId="33" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5874,7 +5969,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46257.698128240743</v>
+        <v>46257.755808796297</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
@@ -8868,29 +8963,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R28">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9043,7 +9138,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9088,7 +9183,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9102,31 +9197,39 @@
   <dimension ref="A1:AG183"/>
   <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" customWidth="1"/>
-    <col min="4" max="4" width="9.296875" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.19921875" customWidth="1"/>
-    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.69921875" customWidth="1"/>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.09765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.296875" customWidth="1"/>
-    <col min="11" max="11" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.796875" customWidth="1"/>
-    <col min="13" max="13" width="26.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.09765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="79.296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.09765625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.09765625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.19921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -9509,25 +9612,25 @@
         <v>661</v>
       </c>
       <c r="Z4" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA4" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB4" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC4" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD4" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE4" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF4" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG4" s="57" t="s">
         <v>674</v>
@@ -9610,25 +9713,25 @@
         <v>661</v>
       </c>
       <c r="Z5" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA5" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB5" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC5" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD5" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE5" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF5" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG5" s="57" t="s">
         <v>674</v>
@@ -9711,25 +9814,25 @@
         <v>661</v>
       </c>
       <c r="Z6" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA6" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB6" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC6" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD6" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE6" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF6" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG6" s="57" t="s">
         <v>674</v>
@@ -9812,25 +9915,25 @@
         <v>661</v>
       </c>
       <c r="Z7" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA7" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB7" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC7" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD7" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE7" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF7" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG7" s="57" t="s">
         <v>674</v>
@@ -9913,25 +10016,25 @@
         <v>661</v>
       </c>
       <c r="Z8" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA8" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB8" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC8" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD8" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE8" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF8" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG8" s="57" t="s">
         <v>674</v>
@@ -10014,25 +10117,25 @@
         <v>661</v>
       </c>
       <c r="Z9" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA9" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB9" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC9" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD9" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE9" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF9" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG9" s="57" t="s">
         <v>674</v>
@@ -10115,25 +10218,25 @@
         <v>661</v>
       </c>
       <c r="Z10" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA10" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB10" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC10" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD10" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE10" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF10" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG10" s="57" t="s">
         <v>674</v>
@@ -10216,25 +10319,25 @@
         <v>661</v>
       </c>
       <c r="Z11" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA11" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB11" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC11" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD11" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE11" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF11" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG11" s="57" t="s">
         <v>674</v>
@@ -10317,25 +10420,25 @@
         <v>661</v>
       </c>
       <c r="Z12" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA12" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB12" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC12" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD12" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE12" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF12" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG12" s="57" t="s">
         <v>674</v>
@@ -10418,25 +10521,25 @@
         <v>661</v>
       </c>
       <c r="Z13" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA13" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB13" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC13" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD13" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE13" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF13" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG13" s="57" t="s">
         <v>674</v>
@@ -10519,25 +10622,25 @@
         <v>661</v>
       </c>
       <c r="Z14" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA14" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB14" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC14" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD14" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE14" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF14" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG14" s="57" t="s">
         <v>674</v>
@@ -10620,25 +10723,25 @@
         <v>661</v>
       </c>
       <c r="Z15" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA15" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB15" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC15" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD15" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE15" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF15" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG15" s="57" t="s">
         <v>674</v>
@@ -10721,25 +10824,25 @@
         <v>661</v>
       </c>
       <c r="Z16" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA16" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB16" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC16" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD16" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE16" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF16" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG16" s="57" t="s">
         <v>674</v>
@@ -10822,25 +10925,25 @@
         <v>661</v>
       </c>
       <c r="Z17" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA17" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB17" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC17" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD17" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE17" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF17" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG17" s="57" t="s">
         <v>674</v>
@@ -10923,25 +11026,25 @@
         <v>661</v>
       </c>
       <c r="Z18" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA18" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB18" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC18" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD18" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE18" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF18" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG18" s="57" t="s">
         <v>674</v>
@@ -11024,25 +11127,25 @@
         <v>661</v>
       </c>
       <c r="Z19" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA19" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB19" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC19" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD19" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE19" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF19" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG19" s="57" t="s">
         <v>674</v>
@@ -11125,25 +11228,25 @@
         <v>661</v>
       </c>
       <c r="Z20" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA20" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB20" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC20" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD20" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE20" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF20" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG20" s="57" t="s">
         <v>674</v>
@@ -11226,25 +11329,25 @@
         <v>661</v>
       </c>
       <c r="Z21" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA21" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB21" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC21" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD21" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE21" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF21" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG21" s="57" t="s">
         <v>674</v>
@@ -11327,25 +11430,25 @@
         <v>661</v>
       </c>
       <c r="Z22" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA22" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB22" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC22" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD22" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE22" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF22" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG22" s="57" t="s">
         <v>674</v>
@@ -11428,25 +11531,25 @@
         <v>661</v>
       </c>
       <c r="Z23" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA23" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB23" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC23" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD23" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE23" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF23" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG23" s="57" t="s">
         <v>674</v>
@@ -11529,25 +11632,25 @@
         <v>661</v>
       </c>
       <c r="Z24" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA24" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB24" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC24" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD24" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE24" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF24" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG24" s="57" t="s">
         <v>674</v>
@@ -11630,25 +11733,25 @@
         <v>661</v>
       </c>
       <c r="Z25" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA25" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB25" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC25" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD25" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE25" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF25" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG25" s="57" t="s">
         <v>674</v>
@@ -11731,25 +11834,25 @@
         <v>661</v>
       </c>
       <c r="Z26" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA26" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB26" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC26" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD26" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE26" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF26" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG26" s="57" t="s">
         <v>674</v>
@@ -11832,25 +11935,25 @@
         <v>661</v>
       </c>
       <c r="Z27" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA27" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB27" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC27" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD27" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE27" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF27" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG27" s="57" t="s">
         <v>674</v>
@@ -11933,25 +12036,25 @@
         <v>661</v>
       </c>
       <c r="Z28" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA28" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB28" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC28" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD28" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE28" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF28" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG28" s="57" t="s">
         <v>674</v>
@@ -12034,25 +12137,25 @@
         <v>661</v>
       </c>
       <c r="Z29" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA29" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB29" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC29" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD29" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE29" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF29" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG29" s="57" t="s">
         <v>674</v>
@@ -12135,25 +12238,25 @@
         <v>661</v>
       </c>
       <c r="Z30" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA30" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB30" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC30" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD30" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE30" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF30" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG30" s="57" t="s">
         <v>674</v>
@@ -12236,25 +12339,25 @@
         <v>661</v>
       </c>
       <c r="Z31" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA31" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB31" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC31" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD31" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE31" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF31" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG31" s="57" t="s">
         <v>674</v>
@@ -12337,25 +12440,25 @@
         <v>661</v>
       </c>
       <c r="Z32" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA32" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB32" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC32" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD32" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE32" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF32" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG32" s="57" t="s">
         <v>674</v>
@@ -12438,25 +12541,25 @@
         <v>661</v>
       </c>
       <c r="Z33" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA33" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB33" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC33" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD33" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE33" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF33" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG33" s="57" t="s">
         <v>674</v>
@@ -12539,25 +12642,25 @@
         <v>661</v>
       </c>
       <c r="Z34" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA34" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB34" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC34" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD34" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE34" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF34" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG34" s="57" t="s">
         <v>674</v>
@@ -12640,25 +12743,25 @@
         <v>661</v>
       </c>
       <c r="Z35" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA35" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB35" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC35" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD35" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE35" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF35" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG35" s="57" t="s">
         <v>674</v>
@@ -12741,25 +12844,25 @@
         <v>661</v>
       </c>
       <c r="Z36" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA36" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB36" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC36" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD36" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE36" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF36" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG36" s="57" t="s">
         <v>674</v>
@@ -12842,25 +12945,25 @@
         <v>661</v>
       </c>
       <c r="Z37" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA37" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB37" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC37" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD37" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE37" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF37" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG37" s="57" t="s">
         <v>674</v>
@@ -12943,25 +13046,25 @@
         <v>661</v>
       </c>
       <c r="Z38" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA38" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB38" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC38" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD38" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE38" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF38" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG38" s="57" t="s">
         <v>674</v>
@@ -13044,25 +13147,25 @@
         <v>661</v>
       </c>
       <c r="Z39" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA39" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB39" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC39" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD39" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE39" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF39" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG39" s="57" t="s">
         <v>674</v>
@@ -13145,25 +13248,25 @@
         <v>661</v>
       </c>
       <c r="Z40" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA40" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB40" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC40" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD40" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE40" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF40" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG40" s="57" t="s">
         <v>674</v>
@@ -13246,25 +13349,25 @@
         <v>661</v>
       </c>
       <c r="Z41" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA41" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB41" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC41" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD41" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE41" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF41" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG41" s="57" t="s">
         <v>674</v>
@@ -13347,25 +13450,25 @@
         <v>661</v>
       </c>
       <c r="Z42" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA42" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB42" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC42" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD42" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE42" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF42" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG42" s="57" t="s">
         <v>674</v>
@@ -13448,25 +13551,25 @@
         <v>661</v>
       </c>
       <c r="Z43" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA43" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB43" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC43" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD43" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE43" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF43" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG43" s="57" t="s">
         <v>674</v>
@@ -13549,25 +13652,25 @@
         <v>661</v>
       </c>
       <c r="Z44" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA44" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB44" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC44" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD44" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE44" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF44" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG44" s="57" t="s">
         <v>674</v>
@@ -13650,25 +13753,25 @@
         <v>661</v>
       </c>
       <c r="Z45" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA45" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB45" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC45" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD45" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE45" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF45" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG45" s="57" t="s">
         <v>674</v>
@@ -13751,25 +13854,25 @@
         <v>661</v>
       </c>
       <c r="Z46" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA46" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB46" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC46" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD46" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE46" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF46" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG46" s="57" t="s">
         <v>674</v>
@@ -13852,25 +13955,25 @@
         <v>661</v>
       </c>
       <c r="Z47" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA47" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB47" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC47" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD47" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE47" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF47" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG47" s="57" t="s">
         <v>674</v>
@@ -13953,25 +14056,25 @@
         <v>661</v>
       </c>
       <c r="Z48" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA48" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB48" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC48" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD48" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE48" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF48" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG48" s="57" t="s">
         <v>674</v>
@@ -14054,25 +14157,25 @@
         <v>661</v>
       </c>
       <c r="Z49" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA49" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB49" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC49" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD49" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE49" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF49" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG49" s="57" t="s">
         <v>674</v>
@@ -14155,25 +14258,25 @@
         <v>661</v>
       </c>
       <c r="Z50" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA50" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB50" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC50" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD50" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE50" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF50" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG50" s="57" t="s">
         <v>674</v>
@@ -14256,25 +14359,25 @@
         <v>661</v>
       </c>
       <c r="Z51" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA51" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB51" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC51" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD51" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE51" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF51" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG51" s="57" t="s">
         <v>674</v>
@@ -14357,25 +14460,25 @@
         <v>661</v>
       </c>
       <c r="Z52" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA52" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB52" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC52" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD52" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE52" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF52" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG52" s="57" t="s">
         <v>674</v>
@@ -14458,25 +14561,25 @@
         <v>661</v>
       </c>
       <c r="Z53" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA53" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB53" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC53" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD53" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE53" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF53" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG53" s="57" t="s">
         <v>674</v>
@@ -14559,25 +14662,25 @@
         <v>661</v>
       </c>
       <c r="Z54" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA54" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB54" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC54" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD54" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE54" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF54" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG54" s="57" t="s">
         <v>674</v>
@@ -14660,25 +14763,25 @@
         <v>661</v>
       </c>
       <c r="Z55" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA55" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB55" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC55" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD55" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE55" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF55" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG55" s="57" t="s">
         <v>674</v>
@@ -14761,25 +14864,25 @@
         <v>661</v>
       </c>
       <c r="Z56" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA56" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB56" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC56" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD56" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE56" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF56" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG56" s="57" t="s">
         <v>674</v>
@@ -14862,25 +14965,25 @@
         <v>661</v>
       </c>
       <c r="Z57" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA57" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB57" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC57" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD57" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE57" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF57" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG57" s="57" t="s">
         <v>674</v>
@@ -14963,25 +15066,25 @@
         <v>661</v>
       </c>
       <c r="Z58" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA58" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB58" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC58" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD58" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE58" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF58" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG58" s="57" t="s">
         <v>674</v>
@@ -15064,25 +15167,25 @@
         <v>661</v>
       </c>
       <c r="Z59" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA59" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB59" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC59" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD59" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE59" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF59" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG59" s="57" t="s">
         <v>674</v>
@@ -15165,25 +15268,25 @@
         <v>661</v>
       </c>
       <c r="Z60" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA60" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB60" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC60" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD60" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE60" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF60" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG60" s="57" t="s">
         <v>674</v>
@@ -15266,25 +15369,25 @@
         <v>661</v>
       </c>
       <c r="Z61" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA61" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB61" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC61" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD61" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE61" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF61" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG61" s="57" t="s">
         <v>674</v>
@@ -15367,25 +15470,25 @@
         <v>661</v>
       </c>
       <c r="Z62" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA62" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB62" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC62" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD62" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE62" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF62" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG62" s="57" t="s">
         <v>674</v>
@@ -15468,25 +15571,25 @@
         <v>661</v>
       </c>
       <c r="Z63" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA63" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB63" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC63" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD63" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE63" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF63" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG63" s="57" t="s">
         <v>674</v>
@@ -15569,25 +15672,25 @@
         <v>661</v>
       </c>
       <c r="Z64" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA64" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB64" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC64" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD64" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE64" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF64" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG64" s="57" t="s">
         <v>674</v>
@@ -15670,25 +15773,25 @@
         <v>661</v>
       </c>
       <c r="Z65" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA65" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB65" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC65" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD65" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE65" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF65" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG65" s="57" t="s">
         <v>674</v>
@@ -15771,25 +15874,25 @@
         <v>661</v>
       </c>
       <c r="Z66" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA66" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB66" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC66" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD66" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE66" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF66" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG66" s="57" t="s">
         <v>674</v>
@@ -15872,25 +15975,25 @@
         <v>661</v>
       </c>
       <c r="Z67" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA67" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB67" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC67" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD67" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE67" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF67" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG67" s="57" t="s">
         <v>674</v>
@@ -15973,25 +16076,25 @@
         <v>661</v>
       </c>
       <c r="Z68" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA68" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB68" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC68" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD68" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE68" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF68" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG68" s="57" t="s">
         <v>674</v>
@@ -16074,25 +16177,25 @@
         <v>661</v>
       </c>
       <c r="Z69" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA69" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB69" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC69" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD69" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE69" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF69" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG69" s="57" t="s">
         <v>674</v>
@@ -16175,25 +16278,25 @@
         <v>661</v>
       </c>
       <c r="Z70" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA70" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB70" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC70" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD70" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE70" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF70" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG70" s="57" t="s">
         <v>674</v>
@@ -16276,25 +16379,25 @@
         <v>661</v>
       </c>
       <c r="Z71" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA71" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB71" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC71" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD71" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE71" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF71" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG71" s="57" t="s">
         <v>674</v>
@@ -16377,25 +16480,25 @@
         <v>661</v>
       </c>
       <c r="Z72" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA72" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB72" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC72" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD72" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE72" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF72" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG72" s="57" t="s">
         <v>674</v>
@@ -16478,25 +16581,25 @@
         <v>661</v>
       </c>
       <c r="Z73" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA73" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB73" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC73" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD73" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE73" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF73" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG73" s="57" t="s">
         <v>674</v>
@@ -16579,25 +16682,25 @@
         <v>661</v>
       </c>
       <c r="Z74" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA74" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB74" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC74" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD74" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE74" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF74" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG74" s="57" t="s">
         <v>674</v>
@@ -16680,25 +16783,25 @@
         <v>661</v>
       </c>
       <c r="Z75" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA75" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB75" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC75" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD75" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE75" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF75" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG75" s="57" t="s">
         <v>674</v>
@@ -16781,25 +16884,25 @@
         <v>661</v>
       </c>
       <c r="Z76" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA76" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB76" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC76" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD76" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE76" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF76" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG76" s="57" t="s">
         <v>674</v>
@@ -16882,25 +16985,25 @@
         <v>661</v>
       </c>
       <c r="Z77" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA77" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB77" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC77" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD77" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE77" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF77" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG77" s="57" t="s">
         <v>674</v>
@@ -16983,25 +17086,25 @@
         <v>661</v>
       </c>
       <c r="Z78" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA78" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB78" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC78" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD78" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE78" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF78" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG78" s="57" t="s">
         <v>674</v>
@@ -17084,25 +17187,25 @@
         <v>661</v>
       </c>
       <c r="Z79" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA79" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB79" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC79" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD79" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE79" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF79" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG79" s="57" t="s">
         <v>674</v>
@@ -17185,25 +17288,25 @@
         <v>661</v>
       </c>
       <c r="Z80" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA80" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB80" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC80" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD80" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE80" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF80" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG80" s="57" t="s">
         <v>674</v>
@@ -17286,25 +17389,25 @@
         <v>661</v>
       </c>
       <c r="Z81" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA81" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB81" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC81" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD81" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE81" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF81" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG81" s="57" t="s">
         <v>674</v>
@@ -17387,25 +17490,25 @@
         <v>661</v>
       </c>
       <c r="Z82" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA82" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB82" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC82" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD82" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE82" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF82" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG82" s="57" t="s">
         <v>674</v>
@@ -17488,25 +17591,25 @@
         <v>661</v>
       </c>
       <c r="Z83" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA83" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB83" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC83" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD83" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE83" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF83" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG83" s="57" t="s">
         <v>674</v>
@@ -17589,25 +17692,25 @@
         <v>661</v>
       </c>
       <c r="Z84" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA84" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB84" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC84" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD84" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE84" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF84" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG84" s="57" t="s">
         <v>674</v>
@@ -17690,25 +17793,25 @@
         <v>661</v>
       </c>
       <c r="Z85" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA85" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB85" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC85" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD85" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE85" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF85" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG85" s="57" t="s">
         <v>674</v>
@@ -17791,25 +17894,25 @@
         <v>661</v>
       </c>
       <c r="Z86" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA86" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB86" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC86" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD86" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE86" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF86" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG86" s="57" t="s">
         <v>674</v>
@@ -17892,25 +17995,25 @@
         <v>661</v>
       </c>
       <c r="Z87" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA87" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB87" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC87" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD87" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE87" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF87" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG87" s="57" t="s">
         <v>674</v>
@@ -17993,25 +18096,25 @@
         <v>661</v>
       </c>
       <c r="Z88" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA88" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB88" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC88" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD88" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE88" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF88" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG88" s="57" t="s">
         <v>674</v>
@@ -18094,25 +18197,25 @@
         <v>661</v>
       </c>
       <c r="Z89" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA89" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB89" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC89" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD89" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE89" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF89" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG89" s="57" t="s">
         <v>674</v>
@@ -18195,25 +18298,25 @@
         <v>661</v>
       </c>
       <c r="Z90" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA90" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB90" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC90" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD90" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE90" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF90" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG90" s="57" t="s">
         <v>674</v>
@@ -18296,25 +18399,25 @@
         <v>661</v>
       </c>
       <c r="Z91" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA91" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB91" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC91" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD91" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE91" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF91" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG91" s="57" t="s">
         <v>674</v>
@@ -18397,25 +18500,25 @@
         <v>661</v>
       </c>
       <c r="Z92" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA92" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB92" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC92" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD92" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE92" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF92" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG92" s="57" t="s">
         <v>674</v>
@@ -18498,25 +18601,25 @@
         <v>661</v>
       </c>
       <c r="Z93" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA93" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB93" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC93" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD93" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE93" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF93" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG93" s="57" t="s">
         <v>674</v>
@@ -18599,25 +18702,25 @@
         <v>661</v>
       </c>
       <c r="Z94" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA94" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB94" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC94" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD94" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE94" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF94" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG94" s="57" t="s">
         <v>674</v>
@@ -18700,25 +18803,25 @@
         <v>661</v>
       </c>
       <c r="Z95" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA95" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB95" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC95" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD95" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE95" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF95" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG95" s="57" t="s">
         <v>674</v>
@@ -18801,25 +18904,25 @@
         <v>661</v>
       </c>
       <c r="Z96" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA96" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB96" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC96" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD96" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE96" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF96" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG96" s="57" t="s">
         <v>674</v>
@@ -18902,25 +19005,25 @@
         <v>661</v>
       </c>
       <c r="Z97" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA97" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB97" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC97" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD97" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE97" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF97" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG97" s="57" t="s">
         <v>674</v>
@@ -19003,25 +19106,25 @@
         <v>661</v>
       </c>
       <c r="Z98" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA98" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB98" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC98" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD98" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE98" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF98" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG98" s="57" t="s">
         <v>674</v>
@@ -19104,25 +19207,25 @@
         <v>661</v>
       </c>
       <c r="Z99" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA99" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB99" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC99" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD99" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE99" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF99" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG99" s="57" t="s">
         <v>674</v>
@@ -19205,25 +19308,25 @@
         <v>661</v>
       </c>
       <c r="Z100" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA100" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB100" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC100" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD100" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE100" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF100" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG100" s="57" t="s">
         <v>674</v>
@@ -19306,25 +19409,25 @@
         <v>661</v>
       </c>
       <c r="Z101" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA101" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB101" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC101" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD101" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE101" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF101" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG101" s="57" t="s">
         <v>674</v>
@@ -19407,25 +19510,25 @@
         <v>661</v>
       </c>
       <c r="Z102" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA102" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB102" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC102" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD102" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE102" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF102" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG102" s="57" t="s">
         <v>674</v>
@@ -19508,25 +19611,25 @@
         <v>661</v>
       </c>
       <c r="Z103" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA103" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB103" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC103" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD103" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE103" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF103" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG103" s="57" t="s">
         <v>674</v>
@@ -19609,25 +19712,25 @@
         <v>661</v>
       </c>
       <c r="Z104" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA104" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB104" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC104" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD104" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE104" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF104" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG104" s="57" t="s">
         <v>674</v>
@@ -19710,25 +19813,25 @@
         <v>661</v>
       </c>
       <c r="Z105" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA105" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB105" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC105" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD105" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE105" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF105" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG105" s="57" t="s">
         <v>674</v>
@@ -19811,25 +19914,25 @@
         <v>661</v>
       </c>
       <c r="Z106" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA106" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB106" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC106" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD106" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE106" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF106" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG106" s="57" t="s">
         <v>674</v>
@@ -19912,25 +20015,25 @@
         <v>661</v>
       </c>
       <c r="Z107" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA107" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB107" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC107" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD107" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE107" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF107" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG107" s="57" t="s">
         <v>674</v>
@@ -20013,25 +20116,25 @@
         <v>661</v>
       </c>
       <c r="Z108" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA108" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB108" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC108" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD108" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE108" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF108" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG108" s="57" t="s">
         <v>674</v>
@@ -20114,25 +20217,25 @@
         <v>661</v>
       </c>
       <c r="Z109" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA109" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB109" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC109" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD109" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE109" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF109" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG109" s="57" t="s">
         <v>674</v>
@@ -20215,25 +20318,25 @@
         <v>661</v>
       </c>
       <c r="Z110" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA110" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB110" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC110" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD110" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE110" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF110" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG110" s="57" t="s">
         <v>674</v>
@@ -20316,25 +20419,25 @@
         <v>661</v>
       </c>
       <c r="Z111" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA111" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB111" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC111" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD111" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE111" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF111" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG111" s="57" t="s">
         <v>674</v>
@@ -20417,25 +20520,25 @@
         <v>661</v>
       </c>
       <c r="Z112" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA112" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB112" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC112" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD112" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE112" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF112" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG112" s="57" t="s">
         <v>674</v>
@@ -20518,25 +20621,25 @@
         <v>661</v>
       </c>
       <c r="Z113" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA113" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB113" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC113" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD113" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE113" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF113" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG113" s="57" t="s">
         <v>674</v>
@@ -20619,25 +20722,25 @@
         <v>661</v>
       </c>
       <c r="Z114" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA114" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB114" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC114" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD114" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE114" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF114" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG114" s="57" t="s">
         <v>674</v>
@@ -20720,25 +20823,25 @@
         <v>661</v>
       </c>
       <c r="Z115" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA115" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB115" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC115" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD115" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE115" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF115" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG115" s="57" t="s">
         <v>674</v>
@@ -20821,25 +20924,25 @@
         <v>661</v>
       </c>
       <c r="Z116" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA116" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB116" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC116" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD116" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE116" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF116" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG116" s="57" t="s">
         <v>674</v>
@@ -20922,25 +21025,25 @@
         <v>661</v>
       </c>
       <c r="Z117" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA117" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB117" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC117" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD117" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE117" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF117" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG117" s="57" t="s">
         <v>674</v>
@@ -21023,25 +21126,25 @@
         <v>661</v>
       </c>
       <c r="Z118" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA118" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB118" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC118" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD118" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE118" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF118" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG118" s="57" t="s">
         <v>674</v>
@@ -21124,25 +21227,25 @@
         <v>661</v>
       </c>
       <c r="Z119" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA119" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB119" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC119" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD119" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE119" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF119" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG119" s="57" t="s">
         <v>674</v>
@@ -21225,25 +21328,25 @@
         <v>661</v>
       </c>
       <c r="Z120" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA120" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB120" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC120" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD120" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE120" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF120" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG120" s="57" t="s">
         <v>674</v>
@@ -21326,25 +21429,25 @@
         <v>661</v>
       </c>
       <c r="Z121" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA121" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB121" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC121" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD121" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE121" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF121" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG121" s="57" t="s">
         <v>674</v>
@@ -21427,25 +21530,25 @@
         <v>661</v>
       </c>
       <c r="Z122" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA122" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB122" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC122" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD122" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE122" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF122" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG122" s="57" t="s">
         <v>674</v>
@@ -21528,25 +21631,25 @@
         <v>661</v>
       </c>
       <c r="Z123" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA123" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB123" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC123" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD123" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE123" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF123" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG123" s="57" t="s">
         <v>674</v>
@@ -21629,25 +21732,25 @@
         <v>661</v>
       </c>
       <c r="Z124" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA124" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB124" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC124" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD124" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE124" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF124" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG124" s="57" t="s">
         <v>674</v>
@@ -21730,25 +21833,25 @@
         <v>661</v>
       </c>
       <c r="Z125" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA125" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB125" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC125" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD125" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE125" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF125" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG125" s="57" t="s">
         <v>674</v>
@@ -21831,25 +21934,25 @@
         <v>661</v>
       </c>
       <c r="Z126" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA126" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB126" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC126" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD126" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE126" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF126" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG126" s="57" t="s">
         <v>674</v>
@@ -21932,25 +22035,25 @@
         <v>661</v>
       </c>
       <c r="Z127" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA127" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB127" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC127" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD127" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE127" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF127" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG127" s="57" t="s">
         <v>674</v>
@@ -22033,25 +22136,25 @@
         <v>661</v>
       </c>
       <c r="Z128" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA128" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB128" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC128" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD128" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE128" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF128" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG128" s="57" t="s">
         <v>674</v>
@@ -22134,25 +22237,25 @@
         <v>661</v>
       </c>
       <c r="Z129" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA129" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB129" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC129" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD129" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE129" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF129" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG129" s="57" t="s">
         <v>674</v>
@@ -22235,25 +22338,25 @@
         <v>661</v>
       </c>
       <c r="Z130" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA130" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB130" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC130" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD130" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE130" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF130" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG130" s="57" t="s">
         <v>674</v>
@@ -22336,25 +22439,25 @@
         <v>661</v>
       </c>
       <c r="Z131" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA131" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB131" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC131" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD131" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE131" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF131" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG131" s="57" t="s">
         <v>674</v>
@@ -22437,25 +22540,25 @@
         <v>661</v>
       </c>
       <c r="Z132" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA132" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB132" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC132" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD132" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE132" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF132" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG132" s="57" t="s">
         <v>674</v>
@@ -22538,25 +22641,25 @@
         <v>661</v>
       </c>
       <c r="Z133" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA133" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB133" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC133" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD133" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE133" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF133" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG133" s="57" t="s">
         <v>674</v>
@@ -22639,25 +22742,25 @@
         <v>661</v>
       </c>
       <c r="Z134" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA134" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB134" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC134" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD134" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE134" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF134" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG134" s="57" t="s">
         <v>674</v>
@@ -22740,25 +22843,25 @@
         <v>661</v>
       </c>
       <c r="Z135" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA135" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB135" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC135" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD135" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE135" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF135" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG135" s="57" t="s">
         <v>674</v>
@@ -22841,25 +22944,25 @@
         <v>661</v>
       </c>
       <c r="Z136" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA136" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB136" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC136" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD136" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE136" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF136" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG136" s="57" t="s">
         <v>674</v>
@@ -22942,25 +23045,25 @@
         <v>661</v>
       </c>
       <c r="Z137" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA137" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB137" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC137" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD137" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE137" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF137" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG137" s="57" t="s">
         <v>674</v>
@@ -23043,25 +23146,25 @@
         <v>661</v>
       </c>
       <c r="Z138" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA138" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB138" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC138" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD138" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE138" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF138" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG138" s="57" t="s">
         <v>674</v>
@@ -23144,25 +23247,25 @@
         <v>661</v>
       </c>
       <c r="Z139" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA139" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB139" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC139" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD139" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE139" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF139" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG139" s="57" t="s">
         <v>674</v>
@@ -23245,25 +23348,25 @@
         <v>661</v>
       </c>
       <c r="Z140" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA140" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB140" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC140" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD140" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE140" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF140" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG140" s="57" t="s">
         <v>674</v>
@@ -23346,25 +23449,25 @@
         <v>661</v>
       </c>
       <c r="Z141" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA141" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB141" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC141" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD141" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE141" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF141" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG141" s="57" t="s">
         <v>674</v>
@@ -23447,25 +23550,25 @@
         <v>661</v>
       </c>
       <c r="Z142" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA142" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB142" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC142" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD142" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE142" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF142" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG142" s="57" t="s">
         <v>674</v>
@@ -23548,25 +23651,25 @@
         <v>661</v>
       </c>
       <c r="Z143" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA143" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB143" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC143" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD143" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE143" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF143" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG143" s="57" t="s">
         <v>674</v>
@@ -23649,25 +23752,25 @@
         <v>661</v>
       </c>
       <c r="Z144" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA144" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB144" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC144" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD144" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE144" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF144" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG144" s="57" t="s">
         <v>674</v>
@@ -23750,25 +23853,25 @@
         <v>661</v>
       </c>
       <c r="Z145" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA145" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB145" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC145" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD145" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE145" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF145" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG145" s="57" t="s">
         <v>674</v>
@@ -23851,25 +23954,25 @@
         <v>661</v>
       </c>
       <c r="Z146" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA146" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB146" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC146" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD146" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE146" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF146" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG146" s="57" t="s">
         <v>674</v>
@@ -23952,25 +24055,25 @@
         <v>661</v>
       </c>
       <c r="Z147" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA147" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB147" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC147" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD147" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE147" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF147" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG147" s="57" t="s">
         <v>674</v>
@@ -24053,25 +24156,25 @@
         <v>661</v>
       </c>
       <c r="Z148" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA148" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB148" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC148" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD148" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE148" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF148" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG148" s="57" t="s">
         <v>674</v>
@@ -24154,25 +24257,25 @@
         <v>661</v>
       </c>
       <c r="Z149" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA149" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB149" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC149" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD149" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE149" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF149" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG149" s="57" t="s">
         <v>674</v>
@@ -24255,25 +24358,25 @@
         <v>661</v>
       </c>
       <c r="Z150" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA150" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB150" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC150" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD150" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE150" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF150" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG150" s="57" t="s">
         <v>674</v>
@@ -24356,25 +24459,25 @@
         <v>661</v>
       </c>
       <c r="Z151" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA151" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB151" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC151" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD151" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE151" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF151" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG151" s="57" t="s">
         <v>674</v>
@@ -24457,25 +24560,25 @@
         <v>661</v>
       </c>
       <c r="Z152" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA152" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB152" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC152" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD152" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE152" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF152" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG152" s="57" t="s">
         <v>674</v>
@@ -24558,25 +24661,25 @@
         <v>661</v>
       </c>
       <c r="Z153" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA153" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB153" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC153" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD153" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE153" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF153" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG153" s="57" t="s">
         <v>674</v>
@@ -24659,25 +24762,25 @@
         <v>661</v>
       </c>
       <c r="Z154" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA154" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB154" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC154" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD154" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE154" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF154" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG154" s="57" t="s">
         <v>674</v>
@@ -24760,25 +24863,25 @@
         <v>661</v>
       </c>
       <c r="Z155" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA155" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB155" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC155" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD155" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE155" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF155" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG155" s="57" t="s">
         <v>674</v>
@@ -24861,25 +24964,25 @@
         <v>661</v>
       </c>
       <c r="Z156" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA156" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB156" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC156" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD156" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE156" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF156" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG156" s="57" t="s">
         <v>674</v>
@@ -24962,25 +25065,25 @@
         <v>661</v>
       </c>
       <c r="Z157" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA157" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB157" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC157" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD157" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE157" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF157" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG157" s="57" t="s">
         <v>674</v>
@@ -25063,25 +25166,25 @@
         <v>661</v>
       </c>
       <c r="Z158" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA158" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB158" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC158" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD158" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE158" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF158" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG158" s="57" t="s">
         <v>674</v>
@@ -25164,25 +25267,25 @@
         <v>661</v>
       </c>
       <c r="Z159" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA159" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB159" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC159" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD159" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE159" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF159" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG159" s="57" t="s">
         <v>674</v>
@@ -25265,25 +25368,25 @@
         <v>661</v>
       </c>
       <c r="Z160" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA160" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB160" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC160" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD160" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE160" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF160" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG160" s="57" t="s">
         <v>674</v>
@@ -25366,25 +25469,25 @@
         <v>661</v>
       </c>
       <c r="Z161" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA161" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB161" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC161" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD161" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE161" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF161" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG161" s="57" t="s">
         <v>674</v>
@@ -25467,25 +25570,25 @@
         <v>661</v>
       </c>
       <c r="Z162" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA162" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB162" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC162" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD162" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE162" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF162" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG162" s="57" t="s">
         <v>674</v>
@@ -25568,25 +25671,25 @@
         <v>661</v>
       </c>
       <c r="Z163" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA163" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB163" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC163" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD163" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE163" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF163" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG163" s="57" t="s">
         <v>674</v>
@@ -25669,25 +25772,25 @@
         <v>661</v>
       </c>
       <c r="Z164" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA164" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB164" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC164" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD164" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE164" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF164" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG164" s="57" t="s">
         <v>674</v>
@@ -25770,25 +25873,25 @@
         <v>661</v>
       </c>
       <c r="Z165" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA165" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB165" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC165" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD165" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE165" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF165" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG165" s="57" t="s">
         <v>674</v>
@@ -25871,25 +25974,25 @@
         <v>661</v>
       </c>
       <c r="Z166" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA166" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB166" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC166" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD166" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE166" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF166" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG166" s="57" t="s">
         <v>674</v>
@@ -25972,25 +26075,25 @@
         <v>661</v>
       </c>
       <c r="Z167" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA167" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB167" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC167" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD167" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE167" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF167" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG167" s="57" t="s">
         <v>674</v>
@@ -26073,25 +26176,25 @@
         <v>661</v>
       </c>
       <c r="Z168" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA168" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB168" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC168" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD168" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE168" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF168" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG168" s="57" t="s">
         <v>674</v>
@@ -26174,25 +26277,25 @@
         <v>661</v>
       </c>
       <c r="Z169" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA169" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB169" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC169" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD169" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE169" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF169" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG169" s="57" t="s">
         <v>674</v>
@@ -26275,25 +26378,25 @@
         <v>661</v>
       </c>
       <c r="Z170" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA170" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB170" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC170" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD170" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE170" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF170" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG170" s="57" t="s">
         <v>674</v>
@@ -26376,25 +26479,25 @@
         <v>661</v>
       </c>
       <c r="Z171" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA171" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB171" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC171" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD171" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE171" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF171" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG171" s="57" t="s">
         <v>674</v>
@@ -26477,25 +26580,25 @@
         <v>661</v>
       </c>
       <c r="Z172" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA172" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB172" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC172" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD172" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE172" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF172" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG172" s="57" t="s">
         <v>674</v>
@@ -26578,25 +26681,25 @@
         <v>661</v>
       </c>
       <c r="Z173" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA173" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB173" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC173" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD173" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE173" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF173" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG173" s="57" t="s">
         <v>674</v>
@@ -26679,25 +26782,25 @@
         <v>661</v>
       </c>
       <c r="Z174" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA174" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB174" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC174" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD174" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE174" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF174" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG174" s="57" t="s">
         <v>674</v>
@@ -26780,25 +26883,25 @@
         <v>661</v>
       </c>
       <c r="Z175" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA175" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB175" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC175" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD175" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE175" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF175" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG175" s="57" t="s">
         <v>674</v>
@@ -26881,25 +26984,25 @@
         <v>661</v>
       </c>
       <c r="Z176" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA176" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB176" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC176" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD176" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE176" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF176" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG176" s="57" t="s">
         <v>674</v>
@@ -26982,25 +27085,25 @@
         <v>661</v>
       </c>
       <c r="Z177" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA177" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB177" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC177" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD177" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE177" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF177" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG177" s="57" t="s">
         <v>674</v>
@@ -27083,25 +27186,25 @@
         <v>661</v>
       </c>
       <c r="Z178" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA178" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB178" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC178" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD178" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE178" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF178" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG178" s="57" t="s">
         <v>674</v>
@@ -27150,14 +27253,15 @@
       <c r="N179" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O179" s="79" t="s">
+      <c r="O179" s="77" t="s">
         <v>664</v>
       </c>
-      <c r="P179" s="73" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q179" s="47" t="s">
-        <v>196</v>
+      <c r="P179" s="79" t="str">
+        <f t="shared" ref="P179:P183" si="0">IF(Q179="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="Q179" s="80" t="s">
+        <v>678</v>
       </c>
       <c r="R179" s="45" t="s">
         <v>196</v>
@@ -27184,25 +27288,25 @@
         <v>661</v>
       </c>
       <c r="Z179" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA179" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB179" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC179" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD179" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE179" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF179" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG179" s="57" t="s">
         <v>674</v>
@@ -27251,14 +27355,15 @@
       <c r="N180" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O180" s="79" t="s">
+      <c r="O180" s="77" t="s">
         <v>667</v>
       </c>
-      <c r="P180" s="73" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q180" s="47" t="s">
-        <v>196</v>
+      <c r="P180" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q180" s="80" t="s">
+        <v>679</v>
       </c>
       <c r="R180" s="45" t="s">
         <v>196</v>
@@ -27285,25 +27390,25 @@
         <v>661</v>
       </c>
       <c r="Z180" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA180" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB180" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC180" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD180" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE180" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF180" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG180" s="57" t="s">
         <v>674</v>
@@ -27352,14 +27457,15 @@
       <c r="N181" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O181" s="79" t="s">
+      <c r="O181" s="77" t="s">
         <v>670</v>
       </c>
-      <c r="P181" s="73" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q181" s="47" t="s">
-        <v>196</v>
+      <c r="P181" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q181" s="80" t="s">
+        <v>680</v>
       </c>
       <c r="R181" s="45" t="s">
         <v>196</v>
@@ -27386,25 +27492,25 @@
         <v>661</v>
       </c>
       <c r="Z181" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA181" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB181" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC181" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD181" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE181" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF181" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG181" s="57" t="s">
         <v>674</v>
@@ -27453,14 +27559,15 @@
       <c r="N182" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O182" s="79" t="s">
+      <c r="O182" s="77" t="s">
         <v>673</v>
       </c>
-      <c r="P182" s="73" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q182" s="47" t="s">
-        <v>196</v>
+      <c r="P182" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q182" s="80" t="s">
+        <v>681</v>
       </c>
       <c r="R182" s="45" t="s">
         <v>196</v>
@@ -27487,25 +27594,25 @@
         <v>661</v>
       </c>
       <c r="Z182" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA182" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB182" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC182" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD182" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE182" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF182" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG182" s="57" t="s">
         <v>674</v>
@@ -27518,67 +27625,68 @@
       <c r="B183" s="16" t="s">
         <v>674</v>
       </c>
-      <c r="C183" s="74" t="s">
+      <c r="C183" s="73" t="s">
         <v>657</v>
       </c>
       <c r="D183" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="E183" s="75" t="s">
+      <c r="E183" s="74" t="s">
         <v>196</v>
       </c>
       <c r="F183" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="G183" s="75" t="s">
+      <c r="G183" s="74" t="s">
         <v>196</v>
       </c>
       <c r="H183" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="I183" s="75" t="s">
+      <c r="I183" s="74" t="s">
         <v>196</v>
       </c>
       <c r="J183" s="36" t="s">
         <v>376</v>
       </c>
-      <c r="K183" s="75" t="s">
+      <c r="K183" s="74" t="s">
         <v>662</v>
       </c>
       <c r="L183" s="36" t="s">
         <v>432</v>
       </c>
-      <c r="M183" s="75" t="s">
+      <c r="M183" s="74" t="s">
         <v>675</v>
       </c>
       <c r="N183" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="O183" s="80" t="s">
+      <c r="O183" s="78" t="s">
         <v>676</v>
       </c>
-      <c r="P183" s="76" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q183" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="R183" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="S183" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="T183" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="U183" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="V183" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="W183" s="77" t="s">
+      <c r="P183" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q183" s="80" t="s">
+        <v>682</v>
+      </c>
+      <c r="R183" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="S183" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="T183" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="U183" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="V183" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="W183" s="75" t="s">
         <v>196</v>
       </c>
       <c r="X183" s="56" t="s">
@@ -27588,25 +27696,25 @@
         <v>661</v>
       </c>
       <c r="Z183" s="56" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA183" s="57" t="s">
         <v>665</v>
       </c>
       <c r="AB183" s="56" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AC183" s="57" t="s">
         <v>668</v>
       </c>
       <c r="AD183" s="56" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AE183" s="57" t="s">
         <v>671</v>
       </c>
       <c r="AF183" s="56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="AG183" s="57" t="s">
         <v>674</v>
@@ -27615,84 +27723,99 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B178 B184:B1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179:B183">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P179:W183">
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+  <conditionalFormatting sqref="R179:W183">
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1 V1 X1 F1 H1 J1 N1 P1 R1">
-    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AG1 T2:W178">
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="25" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y183">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z183">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA183">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB183">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC2:AC183">
+    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AD183">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:AE183">
+    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:AG183">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+  <conditionalFormatting sqref="AF2:AF183">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y183">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AA3">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AC3">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE3">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AG3">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="AG2:AG183">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0384939-9754-4163-B790-9F5B02DC90C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7407ACBB-675B-41A8-BF30-F7DC2C4EFE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2127,19 +2127,19 @@
     <t>é.selecionado.por</t>
   </si>
   <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
-  </si>
-  <si>
-    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
-  </si>
-  <si>
-    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -5767,14 +5767,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43746A7-9034-4253-BBC7-A96C5E7ADA0F}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>182</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>183</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>184</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>189</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>190</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>191</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -5963,19 +5963,19 @@
         <v>447</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46257.755808796297</v>
+        <v>46258.543115046297</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>455</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="39" t="s">
         <v>451</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="39" t="s">
         <v>456</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>181</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>199</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="39" t="s">
         <v>443</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39" t="s">
         <v>584</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="39" t="s">
         <v>586</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="39" t="s">
         <v>588</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="39" t="s">
         <v>590</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="39" t="s">
         <v>592</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="39" t="s">
         <v>594</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="39" t="s">
         <v>596</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="39" t="s">
         <v>598</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="39" t="s">
         <v>600</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="39" t="s">
         <v>602</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="39" t="s">
         <v>604</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>606</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="39" t="s">
         <v>608</v>
       </c>
@@ -6224,36 +6224,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC28"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.296875" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="31" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="61" customWidth="1"/>
     <col min="17" max="17" width="65.5" customWidth="1"/>
-    <col min="18" max="18" width="57.296875" customWidth="1"/>
+    <col min="18" max="18" width="57.33203125" customWidth="1"/>
     <col min="19" max="19" width="5" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="44.796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="30.9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>385</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -7797,7 +7797,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -9000,13 +9000,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7274B-2192-4DC4-A644-E1AD662613FF}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>408</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="24">
         <v>2</v>
       </c>
@@ -9153,13 +9153,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA41B1A8-F6C2-4E23-9DBE-2B95F8FB901A}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.796875" customWidth="1"/>
+    <col min="2" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="27">
         <v>1</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9195,44 +9195,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02829C2B-674F-4380-82F9-2448D015A8F3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:AG183"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.09765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="79.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>194</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -11959,7 +11959,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -12161,7 +12161,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43">
         <v>30</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43">
         <v>31</v>
       </c>
@@ -12363,7 +12363,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="43">
         <v>32</v>
       </c>
@@ -12464,7 +12464,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="43">
         <v>33</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43">
         <v>34</v>
       </c>
@@ -12666,7 +12666,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43">
         <v>35</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43">
         <v>36</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="43">
         <v>37</v>
       </c>
@@ -12969,7 +12969,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="43">
         <v>38</v>
       </c>
@@ -13070,7 +13070,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="43">
         <v>39</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="43">
         <v>40</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="43">
         <v>41</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="43">
         <v>42</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="43">
         <v>43</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="43">
         <v>44</v>
       </c>
@@ -13676,7 +13676,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="43">
         <v>45</v>
       </c>
@@ -13777,7 +13777,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="43">
         <v>46</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="43">
         <v>47</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="43">
         <v>48</v>
       </c>
@@ -14080,7 +14080,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="43">
         <v>49</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="43">
         <v>50</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="43">
         <v>51</v>
       </c>
@@ -14383,7 +14383,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="43">
         <v>52</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="43">
         <v>53</v>
       </c>
@@ -14585,7 +14585,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="43">
         <v>54</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="43">
         <v>55</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="43">
         <v>56</v>
       </c>
@@ -14888,7 +14888,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="43">
         <v>57</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="43">
         <v>58</v>
       </c>
@@ -15090,7 +15090,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="43">
         <v>59</v>
       </c>
@@ -15191,7 +15191,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="43">
         <v>60</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="43">
         <v>61</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="43">
         <v>62</v>
       </c>
@@ -15494,7 +15494,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="43">
         <v>63</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="43">
         <v>64</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43">
         <v>65</v>
       </c>
@@ -15797,7 +15797,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="43">
         <v>66</v>
       </c>
@@ -15898,7 +15898,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="43">
         <v>67</v>
       </c>
@@ -15999,7 +15999,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="43">
         <v>68</v>
       </c>
@@ -16100,7 +16100,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="43">
         <v>69</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="43">
         <v>70</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="43">
         <v>71</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="43">
         <v>72</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="43">
         <v>73</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="43">
         <v>74</v>
       </c>
@@ -16706,7 +16706,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="43">
         <v>75</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="43">
         <v>76</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="43">
         <v>77</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="43">
         <v>78</v>
       </c>
@@ -17110,7 +17110,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="43">
         <v>79</v>
       </c>
@@ -17211,7 +17211,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="43">
         <v>80</v>
       </c>
@@ -17312,7 +17312,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="43">
         <v>81</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="43">
         <v>82</v>
       </c>
@@ -17514,7 +17514,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="43">
         <v>83</v>
       </c>
@@ -17615,7 +17615,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="43">
         <v>84</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="43">
         <v>85</v>
       </c>
@@ -17817,7 +17817,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="43">
         <v>86</v>
       </c>
@@ -17918,7 +17918,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="43">
         <v>87</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="43">
         <v>88</v>
       </c>
@@ -18120,7 +18120,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="43">
         <v>89</v>
       </c>
@@ -18221,7 +18221,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="43">
         <v>90</v>
       </c>
@@ -18322,7 +18322,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="43">
         <v>91</v>
       </c>
@@ -18423,7 +18423,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="43">
         <v>92</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="43">
         <v>93</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="43">
         <v>94</v>
       </c>
@@ -18726,7 +18726,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="43">
         <v>95</v>
       </c>
@@ -18827,7 +18827,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="43">
         <v>96</v>
       </c>
@@ -18928,7 +18928,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="43">
         <v>97</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="43">
         <v>98</v>
       </c>
@@ -19130,7 +19130,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="43">
         <v>99</v>
       </c>
@@ -19231,7 +19231,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="43">
         <v>100</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="43">
         <v>101</v>
       </c>
@@ -19433,7 +19433,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="43">
         <v>102</v>
       </c>
@@ -19534,7 +19534,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="43">
         <v>103</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="43">
         <v>104</v>
       </c>
@@ -19736,7 +19736,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="43">
         <v>105</v>
       </c>
@@ -19837,7 +19837,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="43">
         <v>106</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="43">
         <v>107</v>
       </c>
@@ -20039,7 +20039,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="43">
         <v>108</v>
       </c>
@@ -20140,7 +20140,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="43">
         <v>109</v>
       </c>
@@ -20241,7 +20241,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="43">
         <v>110</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="43">
         <v>111</v>
       </c>
@@ -20443,7 +20443,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="43">
         <v>112</v>
       </c>
@@ -20544,7 +20544,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="43">
         <v>113</v>
       </c>
@@ -20645,7 +20645,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="43">
         <v>114</v>
       </c>
@@ -20746,7 +20746,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="43">
         <v>115</v>
       </c>
@@ -20847,7 +20847,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="43">
         <v>116</v>
       </c>
@@ -20948,7 +20948,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="43">
         <v>117</v>
       </c>
@@ -21049,7 +21049,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="43">
         <v>118</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="43">
         <v>119</v>
       </c>
@@ -21251,7 +21251,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="43">
         <v>120</v>
       </c>
@@ -21352,7 +21352,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="43">
         <v>121</v>
       </c>
@@ -21453,7 +21453,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="43">
         <v>122</v>
       </c>
@@ -21554,7 +21554,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="43">
         <v>123</v>
       </c>
@@ -21655,7 +21655,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="43">
         <v>124</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="43">
         <v>125</v>
       </c>
@@ -21857,7 +21857,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="43">
         <v>126</v>
       </c>
@@ -21958,7 +21958,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="43">
         <v>127</v>
       </c>
@@ -22059,7 +22059,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="43">
         <v>128</v>
       </c>
@@ -22160,7 +22160,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="43">
         <v>129</v>
       </c>
@@ -22261,7 +22261,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="43">
         <v>130</v>
       </c>
@@ -22362,7 +22362,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="43">
         <v>131</v>
       </c>
@@ -22463,7 +22463,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="43">
         <v>132</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="43">
         <v>133</v>
       </c>
@@ -22665,7 +22665,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="43">
         <v>134</v>
       </c>
@@ -22766,7 +22766,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="43">
         <v>135</v>
       </c>
@@ -22867,7 +22867,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="43">
         <v>136</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="43">
         <v>137</v>
       </c>
@@ -23069,7 +23069,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="43">
         <v>138</v>
       </c>
@@ -23170,7 +23170,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="43">
         <v>139</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="43">
         <v>140</v>
       </c>
@@ -23372,7 +23372,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="43">
         <v>141</v>
       </c>
@@ -23473,7 +23473,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="43">
         <v>142</v>
       </c>
@@ -23574,7 +23574,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="43">
         <v>143</v>
       </c>
@@ -23675,7 +23675,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="43">
         <v>144</v>
       </c>
@@ -23776,7 +23776,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="43">
         <v>145</v>
       </c>
@@ -23877,7 +23877,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="43">
         <v>146</v>
       </c>
@@ -23978,7 +23978,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="43">
         <v>147</v>
       </c>
@@ -24079,7 +24079,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="43">
         <v>148</v>
       </c>
@@ -24180,7 +24180,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="43">
         <v>149</v>
       </c>
@@ -24281,7 +24281,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="43">
         <v>150</v>
       </c>
@@ -24382,7 +24382,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="43">
         <v>151</v>
       </c>
@@ -24483,7 +24483,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="43">
         <v>152</v>
       </c>
@@ -24584,7 +24584,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="43">
         <v>153</v>
       </c>
@@ -24685,7 +24685,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="43">
         <v>154</v>
       </c>
@@ -24786,7 +24786,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="43">
         <v>155</v>
       </c>
@@ -24887,7 +24887,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="43">
         <v>156</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="43">
         <v>157</v>
       </c>
@@ -25089,7 +25089,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="43">
         <v>158</v>
       </c>
@@ -25190,7 +25190,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="43">
         <v>159</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="43">
         <v>160</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="43">
         <v>161</v>
       </c>
@@ -25493,7 +25493,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="43">
         <v>162</v>
       </c>
@@ -25594,7 +25594,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="43">
         <v>163</v>
       </c>
@@ -25695,7 +25695,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="43">
         <v>164</v>
       </c>
@@ -25796,7 +25796,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="43">
         <v>165</v>
       </c>
@@ -25897,7 +25897,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="43">
         <v>166</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="43">
         <v>167</v>
       </c>
@@ -26099,7 +26099,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="43">
         <v>168</v>
       </c>
@@ -26200,7 +26200,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="43">
         <v>169</v>
       </c>
@@ -26301,7 +26301,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="43">
         <v>170</v>
       </c>
@@ -26402,7 +26402,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="43">
         <v>171</v>
       </c>
@@ -26503,7 +26503,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="43">
         <v>172</v>
       </c>
@@ -26604,7 +26604,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="43">
         <v>173</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="43">
         <v>174</v>
       </c>
@@ -26806,7 +26806,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="43">
         <v>175</v>
       </c>
@@ -26907,7 +26907,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="43">
         <v>176</v>
       </c>
@@ -27008,7 +27008,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="43">
         <v>177</v>
       </c>
@@ -27109,7 +27109,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="43">
         <v>178</v>
       </c>
@@ -27210,7 +27210,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="179" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="43">
         <v>179</v>
       </c>
@@ -27312,7 +27312,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="180" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="43">
         <v>180</v>
       </c>
@@ -27414,7 +27414,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="181" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="43">
         <v>181</v>
       </c>
@@ -27516,7 +27516,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="182" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="43">
         <v>182</v>
       </c>
@@ -27618,7 +27618,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="183" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="43">
         <v>183</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7407ACBB-675B-41A8-BF30-F7DC2C4EFE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0938868-2BBA-4ECE-8701-143CFA150841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5767,14 +5767,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43746A7-9034-4253-BBC7-A96C5E7ADA0F}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>182</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>183</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>184</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>189</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>190</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>191</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -5963,19 +5963,19 @@
         <v>447</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46258.543115046297</v>
+        <v>46264.561311921294</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>455</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>451</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>456</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>181</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>199</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>443</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>584</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>586</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>588</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
         <v>590</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
         <v>592</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
         <v>594</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
         <v>596</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
         <v>598</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
         <v>600</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>602</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
         <v>604</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>606</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>608</v>
       </c>
@@ -6224,36 +6224,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC28"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.296875" style="31" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.296875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="61" customWidth="1"/>
     <col min="17" max="17" width="65.5" customWidth="1"/>
-    <col min="18" max="18" width="57.33203125" customWidth="1"/>
+    <col min="18" max="18" width="57.296875" customWidth="1"/>
     <col min="19" max="19" width="5" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>385</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -7797,7 +7797,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -8875,10 +8875,10 @@
         <v>654</v>
       </c>
       <c r="D28" s="30" t="s">
+        <v>656</v>
+      </c>
+      <c r="E28" s="30" t="s">
         <v>655</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>656</v>
       </c>
       <c r="F28" s="30" t="s">
         <v>657</v>
@@ -8904,11 +8904,11 @@
       </c>
       <c r="M28" s="52" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N28" s="52" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O28" s="52" t="str">
         <f t="shared" si="11"/>
@@ -8932,11 +8932,11 @@
       </c>
       <c r="U28" s="38" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V28" s="53" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W28" s="38" t="s">
         <v>471</v>
@@ -9000,13 +9000,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7274B-2192-4DC4-A644-E1AD662613FF}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>408</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="24">
         <v>2</v>
       </c>
@@ -9153,13 +9153,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA41B1A8-F6C2-4E23-9DBE-2B95F8FB901A}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="27">
         <v>1</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9195,44 +9195,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02829C2B-674F-4380-82F9-2448D015A8F3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:AG183"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>194</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -11959,7 +11959,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -12161,7 +12161,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="43">
         <v>30</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="43">
         <v>31</v>
       </c>
@@ -12363,7 +12363,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="43">
         <v>32</v>
       </c>
@@ -12464,7 +12464,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="43">
         <v>33</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="43">
         <v>34</v>
       </c>
@@ -12666,7 +12666,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="43">
         <v>35</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="43">
         <v>36</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="43">
         <v>37</v>
       </c>
@@ -12969,7 +12969,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="43">
         <v>38</v>
       </c>
@@ -13070,7 +13070,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="43">
         <v>39</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="43">
         <v>40</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="43">
         <v>41</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="43">
         <v>42</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="43">
         <v>43</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="43">
         <v>44</v>
       </c>
@@ -13676,7 +13676,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="43">
         <v>45</v>
       </c>
@@ -13777,7 +13777,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="43">
         <v>46</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="43">
         <v>47</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="43">
         <v>48</v>
       </c>
@@ -14080,7 +14080,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="43">
         <v>49</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="43">
         <v>50</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="43">
         <v>51</v>
       </c>
@@ -14383,7 +14383,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="43">
         <v>52</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="43">
         <v>53</v>
       </c>
@@ -14585,7 +14585,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="43">
         <v>54</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="43">
         <v>55</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="43">
         <v>56</v>
       </c>
@@ -14888,7 +14888,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="43">
         <v>57</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="43">
         <v>58</v>
       </c>
@@ -15090,7 +15090,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="43">
         <v>59</v>
       </c>
@@ -15191,7 +15191,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="43">
         <v>60</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="43">
         <v>61</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="43">
         <v>62</v>
       </c>
@@ -15494,7 +15494,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="43">
         <v>63</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="43">
         <v>64</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="43">
         <v>65</v>
       </c>
@@ -15797,7 +15797,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="43">
         <v>66</v>
       </c>
@@ -15898,7 +15898,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="43">
         <v>67</v>
       </c>
@@ -15999,7 +15999,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="43">
         <v>68</v>
       </c>
@@ -16100,7 +16100,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="43">
         <v>69</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="43">
         <v>70</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="43">
         <v>71</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="43">
         <v>72</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="43">
         <v>73</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="43">
         <v>74</v>
       </c>
@@ -16706,7 +16706,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="43">
         <v>75</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="43">
         <v>76</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="43">
         <v>77</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="43">
         <v>78</v>
       </c>
@@ -17110,7 +17110,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="43">
         <v>79</v>
       </c>
@@ -17211,7 +17211,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="43">
         <v>80</v>
       </c>
@@ -17312,7 +17312,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="43">
         <v>81</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="43">
         <v>82</v>
       </c>
@@ -17514,7 +17514,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="43">
         <v>83</v>
       </c>
@@ -17615,7 +17615,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="43">
         <v>84</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="43">
         <v>85</v>
       </c>
@@ -17817,7 +17817,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="43">
         <v>86</v>
       </c>
@@ -17918,7 +17918,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="43">
         <v>87</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="43">
         <v>88</v>
       </c>
@@ -18120,7 +18120,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="43">
         <v>89</v>
       </c>
@@ -18221,7 +18221,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="43">
         <v>90</v>
       </c>
@@ -18322,7 +18322,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="43">
         <v>91</v>
       </c>
@@ -18423,7 +18423,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="43">
         <v>92</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="43">
         <v>93</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="43">
         <v>94</v>
       </c>
@@ -18726,7 +18726,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="43">
         <v>95</v>
       </c>
@@ -18827,7 +18827,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="43">
         <v>96</v>
       </c>
@@ -18928,7 +18928,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="43">
         <v>97</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="43">
         <v>98</v>
       </c>
@@ -19130,7 +19130,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="43">
         <v>99</v>
       </c>
@@ -19231,7 +19231,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="43">
         <v>100</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="43">
         <v>101</v>
       </c>
@@ -19433,7 +19433,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="43">
         <v>102</v>
       </c>
@@ -19534,7 +19534,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="43">
         <v>103</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="43">
         <v>104</v>
       </c>
@@ -19736,7 +19736,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="43">
         <v>105</v>
       </c>
@@ -19837,7 +19837,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="43">
         <v>106</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="43">
         <v>107</v>
       </c>
@@ -20039,7 +20039,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="43">
         <v>108</v>
       </c>
@@ -20140,7 +20140,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="43">
         <v>109</v>
       </c>
@@ -20241,7 +20241,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="43">
         <v>110</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="43">
         <v>111</v>
       </c>
@@ -20443,7 +20443,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="43">
         <v>112</v>
       </c>
@@ -20544,7 +20544,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="43">
         <v>113</v>
       </c>
@@ -20645,7 +20645,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="43">
         <v>114</v>
       </c>
@@ -20746,7 +20746,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="43">
         <v>115</v>
       </c>
@@ -20847,7 +20847,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="43">
         <v>116</v>
       </c>
@@ -20948,7 +20948,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="43">
         <v>117</v>
       </c>
@@ -21049,7 +21049,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="43">
         <v>118</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="43">
         <v>119</v>
       </c>
@@ -21251,7 +21251,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="43">
         <v>120</v>
       </c>
@@ -21352,7 +21352,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="43">
         <v>121</v>
       </c>
@@ -21453,7 +21453,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="43">
         <v>122</v>
       </c>
@@ -21554,7 +21554,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="43">
         <v>123</v>
       </c>
@@ -21655,7 +21655,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="43">
         <v>124</v>
       </c>
@@ -21756,7 +21756,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="43">
         <v>125</v>
       </c>
@@ -21857,7 +21857,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="43">
         <v>126</v>
       </c>
@@ -21958,7 +21958,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="43">
         <v>127</v>
       </c>
@@ -22059,7 +22059,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="43">
         <v>128</v>
       </c>
@@ -22160,7 +22160,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="43">
         <v>129</v>
       </c>
@@ -22261,7 +22261,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="43">
         <v>130</v>
       </c>
@@ -22362,7 +22362,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="43">
         <v>131</v>
       </c>
@@ -22463,7 +22463,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="43">
         <v>132</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="43">
         <v>133</v>
       </c>
@@ -22665,7 +22665,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="43">
         <v>134</v>
       </c>
@@ -22766,7 +22766,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="43">
         <v>135</v>
       </c>
@@ -22867,7 +22867,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="43">
         <v>136</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="43">
         <v>137</v>
       </c>
@@ -23069,7 +23069,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="43">
         <v>138</v>
       </c>
@@ -23170,7 +23170,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="43">
         <v>139</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="43">
         <v>140</v>
       </c>
@@ -23372,7 +23372,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="43">
         <v>141</v>
       </c>
@@ -23473,7 +23473,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="43">
         <v>142</v>
       </c>
@@ -23574,7 +23574,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="43">
         <v>143</v>
       </c>
@@ -23675,7 +23675,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="43">
         <v>144</v>
       </c>
@@ -23776,7 +23776,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="43">
         <v>145</v>
       </c>
@@ -23877,7 +23877,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="43">
         <v>146</v>
       </c>
@@ -23978,7 +23978,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="43">
         <v>147</v>
       </c>
@@ -24079,7 +24079,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="43">
         <v>148</v>
       </c>
@@ -24180,7 +24180,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="43">
         <v>149</v>
       </c>
@@ -24281,7 +24281,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="43">
         <v>150</v>
       </c>
@@ -24382,7 +24382,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="43">
         <v>151</v>
       </c>
@@ -24483,7 +24483,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="43">
         <v>152</v>
       </c>
@@ -24584,7 +24584,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43">
         <v>153</v>
       </c>
@@ -24685,7 +24685,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="43">
         <v>154</v>
       </c>
@@ -24786,7 +24786,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="43">
         <v>155</v>
       </c>
@@ -24887,7 +24887,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="43">
         <v>156</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="43">
         <v>157</v>
       </c>
@@ -25089,7 +25089,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="43">
         <v>158</v>
       </c>
@@ -25190,7 +25190,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="43">
         <v>159</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="43">
         <v>160</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="43">
         <v>161</v>
       </c>
@@ -25493,7 +25493,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="43">
         <v>162</v>
       </c>
@@ -25594,7 +25594,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="43">
         <v>163</v>
       </c>
@@ -25695,7 +25695,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="43">
         <v>164</v>
       </c>
@@ -25796,7 +25796,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="43">
         <v>165</v>
       </c>
@@ -25897,7 +25897,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="43">
         <v>166</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="43">
         <v>167</v>
       </c>
@@ -26099,7 +26099,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="43">
         <v>168</v>
       </c>
@@ -26200,7 +26200,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="43">
         <v>169</v>
       </c>
@@ -26301,7 +26301,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="43">
         <v>170</v>
       </c>
@@ -26402,7 +26402,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="43">
         <v>171</v>
       </c>
@@ -26503,7 +26503,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="43">
         <v>172</v>
       </c>
@@ -26604,7 +26604,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="43">
         <v>173</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="43">
         <v>174</v>
       </c>
@@ -26806,7 +26806,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="43">
         <v>175</v>
       </c>
@@ -26907,7 +26907,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="43">
         <v>176</v>
       </c>
@@ -27008,7 +27008,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="43">
         <v>177</v>
       </c>
@@ -27109,7 +27109,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="43">
         <v>178</v>
       </c>
@@ -27210,7 +27210,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="179" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="43">
         <v>179</v>
       </c>
@@ -27312,7 +27312,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="180" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="43">
         <v>180</v>
       </c>
@@ -27414,7 +27414,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="181" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="43">
         <v>181</v>
       </c>
@@ -27516,7 +27516,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="182" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="43">
         <v>182</v>
       </c>
@@ -27618,7 +27618,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="183" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:33" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="43">
         <v>183</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810811EF-2381-4335-80ED-765A2D4CDCAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912C0C1C-7650-469B-B539-708ED9149C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6658" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6690" uniqueCount="701">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2191,6 +2191,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2822,14 +2825,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color theme="0"/>
       </font>
     </dxf>
@@ -3083,6 +3078,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -6030,7 +6033,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46268.493541203701</v>
+        <v>46268.687810416668</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
@@ -6284,7 +6287,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
@@ -6312,9 +6315,10 @@
     <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.5" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="57.75" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>385</v>
       </c>
@@ -6402,8 +6406,11 @@
       <c r="AC1" s="20" t="s">
         <v>407</v>
       </c>
+      <c r="AD1" s="20" t="s">
+        <v>700</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -6499,8 +6506,11 @@
       <c r="AC2" s="38" t="s">
         <v>472</v>
       </c>
+      <c r="AD2" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -6596,8 +6606,11 @@
       <c r="AC3" s="38" t="s">
         <v>473</v>
       </c>
+      <c r="AD3" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -6693,8 +6706,11 @@
       <c r="AC4" s="38" t="s">
         <v>377</v>
       </c>
+      <c r="AD4" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -6790,8 +6806,11 @@
       <c r="AC5" s="38" t="s">
         <v>474</v>
       </c>
+      <c r="AD5" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -6887,8 +6906,11 @@
       <c r="AC6" s="38" t="s">
         <v>475</v>
       </c>
+      <c r="AD6" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -6984,8 +7006,11 @@
       <c r="AC7" s="38" t="s">
         <v>476</v>
       </c>
+      <c r="AD7" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -7081,8 +7106,11 @@
       <c r="AC8" s="38" t="s">
         <v>477</v>
       </c>
+      <c r="AD8" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -7178,8 +7206,11 @@
       <c r="AC9" s="38" t="s">
         <v>478</v>
       </c>
+      <c r="AD9" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -7275,8 +7306,11 @@
       <c r="AC10" s="38" t="s">
         <v>479</v>
       </c>
+      <c r="AD10" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -7372,8 +7406,11 @@
       <c r="AC11" s="38" t="s">
         <v>480</v>
       </c>
+      <c r="AD11" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -7469,8 +7506,11 @@
       <c r="AC12" s="38" t="s">
         <v>481</v>
       </c>
+      <c r="AD12" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -7566,8 +7606,11 @@
       <c r="AC13" s="38" t="s">
         <v>482</v>
       </c>
+      <c r="AD13" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -7663,8 +7706,11 @@
       <c r="AC14" s="38" t="s">
         <v>483</v>
       </c>
+      <c r="AD14" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -7760,8 +7806,11 @@
       <c r="AC15" s="53" t="s">
         <v>527</v>
       </c>
+      <c r="AD15" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -7857,8 +7906,11 @@
       <c r="AC16" s="53" t="s">
         <v>534</v>
       </c>
+      <c r="AD16" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -7954,8 +8006,11 @@
       <c r="AC17" s="53" t="s">
         <v>529</v>
       </c>
+      <c r="AD17" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -8051,8 +8106,11 @@
       <c r="AC18" s="53" t="s">
         <v>530</v>
       </c>
+      <c r="AD18" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -8148,8 +8206,11 @@
       <c r="AC19" s="53" t="s">
         <v>531</v>
       </c>
+      <c r="AD19" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -8245,8 +8306,11 @@
       <c r="AC20" s="53" t="s">
         <v>532</v>
       </c>
+      <c r="AD20" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -8342,8 +8406,11 @@
       <c r="AC21" s="53" t="s">
         <v>533</v>
       </c>
+      <c r="AD21" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -8439,8 +8506,11 @@
       <c r="AC22" s="53" t="s">
         <v>536</v>
       </c>
+      <c r="AD22" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -8536,8 +8606,11 @@
       <c r="AC23" s="53" t="s">
         <v>537</v>
       </c>
+      <c r="AD23" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -8633,8 +8706,11 @@
       <c r="AC24" s="53" t="s">
         <v>535</v>
       </c>
+      <c r="AD24" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -8730,8 +8806,11 @@
       <c r="AC25" s="53" t="s">
         <v>540</v>
       </c>
+      <c r="AD25" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -8827,8 +8906,11 @@
       <c r="AC26" s="53" t="s">
         <v>528</v>
       </c>
+      <c r="AD26" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -8924,8 +9006,11 @@
       <c r="AC27" s="53" t="s">
         <v>539</v>
       </c>
+      <c r="AD27" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -9021,8 +9106,11 @@
       <c r="AC28" s="70" t="s">
         <v>196</v>
       </c>
+      <c r="AD28" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -9118,8 +9206,11 @@
       <c r="AC29" s="70" t="s">
         <v>196</v>
       </c>
+      <c r="AD29" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -9215,8 +9306,11 @@
       <c r="AC30" s="70" t="s">
         <v>196</v>
       </c>
+      <c r="AD30" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -9312,8 +9406,11 @@
       <c r="AC31" s="70" t="s">
         <v>196</v>
       </c>
+      <c r="AD31" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -9409,41 +9506,44 @@
       <c r="AC32" s="70" t="s">
         <v>196</v>
       </c>
+      <c r="AD32" s="70" t="s">
+        <v>196</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B32">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:F32">
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="31" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="30" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F31">
-    <cfRule type="duplicateValues" dxfId="26" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R27">
-    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="S1:X1 AD1:XFD1 A33:Q1048576 A1:Q1 S33:Y1048576 AA33:AA1048576 AC33:XFD1048576" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AF1:XFD1 A33:Q1048576 A1:Q1 S33:Y1048576 AA33:AA1048576 AC33:AC1048576 AE33:XFD1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9590,7 +9690,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9635,7 +9735,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28175,99 +28275,99 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B178 B184:B1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179:B183">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="18" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="17" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R179:W183">
-    <cfRule type="cellIs" dxfId="16" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1 V1 X1 F1 H1 J1 N1 P1 R1">
-    <cfRule type="cellIs" dxfId="15" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AG1 T2:W178">
-    <cfRule type="cellIs" dxfId="14" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Y183">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z183">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA183">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB183">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC183">
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD183">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE183">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF183">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG183">
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAF4555-4469-4020-ABA3-4C3C53D1D346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CB72E3-5F8C-48D5-A78A-E5EB34286C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6725" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6725" uniqueCount="711">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2047,9 +2047,6 @@
   </si>
   <si>
     <t>Atributo Ifc</t>
-  </si>
-  <si>
-    <t>API.Revit</t>
   </si>
   <si>
     <t>API_Ambiente</t>
@@ -2596,7 +2593,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2803,9 +2800,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2842,15 +2836,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="109">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="128">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2881,6 +2867,142 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2901,11 +3023,33 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3181,6 +3325,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5567,41 +5719,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:AG183" headerRowCount="0" totalsRowShown="0" headerRowDxfId="108" headerRowBorderDxfId="107" tableBorderDxfId="106" totalsRowBorderDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:AG183" headerRowCount="0" totalsRowShown="0" headerRowDxfId="127" headerRowBorderDxfId="126" tableBorderDxfId="125" totalsRowBorderDxfId="124">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="104" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="102" dataDxfId="101"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="100" dataDxfId="99"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="98" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="96" dataDxfId="95"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="94" dataDxfId="93"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="92" dataDxfId="91"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="90" dataDxfId="89"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="88" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="86" dataDxfId="85"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="84" dataDxfId="83"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="82" dataDxfId="81"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="80" dataDxfId="79"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="78" dataDxfId="77"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="76" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="26" xr3:uid="{364EAD9F-B4D7-43DB-A456-E20A3CB3829E}" name="Coluna21" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="27" xr3:uid="{0295ED4C-EACC-4AE2-9685-0BAC96EB0ECA}" name="Coluna22" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="28" xr3:uid="{FA29F4FB-AC77-4D38-9885-60A710F77062}" name="Coluna23" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="29" xr3:uid="{A7FAABAE-4A27-4FF5-B0DD-8D1252FAF81E}" name="Coluna24" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="30" xr3:uid="{D98E6886-A8CD-454E-A6E0-0CFCFBAAA7E8}" name="Coluna25" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="31" xr3:uid="{45B42935-10EC-4D9E-8FE5-A6973C46330A}" name="Coluna26" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="32" xr3:uid="{BAA53309-A49A-4131-A521-AABC6126A49F}" name="Coluna27" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="33" xr3:uid="{D12E34CA-3D33-4D44-A383-CFF16E015D81}" name="Coluna28" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="123" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="121" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="119" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="117" dataDxfId="116"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="115" dataDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="113" dataDxfId="112"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="111" dataDxfId="110"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="109" dataDxfId="108"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="107" dataDxfId="106"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="105" dataDxfId="104"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="103" dataDxfId="102"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="101" dataDxfId="100"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="99" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="97" dataDxfId="96"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="93" dataDxfId="92"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="91" dataDxfId="90"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="26" xr3:uid="{364EAD9F-B4D7-43DB-A456-E20A3CB3829E}" name="Coluna21" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="27" xr3:uid="{0295ED4C-EACC-4AE2-9685-0BAC96EB0ECA}" name="Coluna22" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="28" xr3:uid="{FA29F4FB-AC77-4D38-9885-60A710F77062}" name="Coluna23" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="29" xr3:uid="{A7FAABAE-4A27-4FF5-B0DD-8D1252FAF81E}" name="Coluna24" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="30" xr3:uid="{D98E6886-A8CD-454E-A6E0-0CFCFBAAA7E8}" name="Coluna25" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="31" xr3:uid="{45B42935-10EC-4D9E-8FE5-A6973C46330A}" name="Coluna26" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="32" xr3:uid="{BAA53309-A49A-4131-A521-AABC6126A49F}" name="Coluna27" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="33" xr3:uid="{D12E34CA-3D33-4D44-A383-CFF16E015D81}" name="Coluna28" headerRowDxfId="59" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -6128,7 +6280,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46273.465476736113</v>
+        <v>46273.507975231485</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
@@ -6399,7 +6551,7 @@
     <col min="16" max="16" width="61" customWidth="1"/>
     <col min="17" max="17" width="65.5" customWidth="1"/>
     <col min="18" max="18" width="57.33203125" customWidth="1"/>
-    <col min="19" max="19" width="5" style="82" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" style="81" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
@@ -6502,7 +6654,7 @@
         <v>407</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6564,7 +6716,7 @@
       <c r="R2" s="55" t="s">
         <v>547</v>
       </c>
-      <c r="S2" s="80" t="s">
+      <c r="S2" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T2" s="53" t="str">
@@ -6664,7 +6816,7 @@
       <c r="R3" s="55" t="s">
         <v>550</v>
       </c>
-      <c r="S3" s="80" t="s">
+      <c r="S3" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T3" s="53" t="str">
@@ -6764,7 +6916,7 @@
       <c r="R4" s="55" t="s">
         <v>553</v>
       </c>
-      <c r="S4" s="80" t="s">
+      <c r="S4" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T4" s="53" t="str">
@@ -6864,7 +7016,7 @@
       <c r="R5" s="55" t="s">
         <v>556</v>
       </c>
-      <c r="S5" s="80" t="s">
+      <c r="S5" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T5" s="53" t="str">
@@ -6964,7 +7116,7 @@
       <c r="R6" s="55" t="s">
         <v>559</v>
       </c>
-      <c r="S6" s="80" t="s">
+      <c r="S6" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T6" s="53" t="str">
@@ -7064,7 +7216,7 @@
       <c r="R7" s="55" t="s">
         <v>562</v>
       </c>
-      <c r="S7" s="80" t="s">
+      <c r="S7" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T7" s="53" t="str">
@@ -7164,7 +7316,7 @@
       <c r="R8" s="55" t="s">
         <v>565</v>
       </c>
-      <c r="S8" s="80" t="s">
+      <c r="S8" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T8" s="53" t="str">
@@ -7264,7 +7416,7 @@
       <c r="R9" s="55" t="s">
         <v>568</v>
       </c>
-      <c r="S9" s="80" t="s">
+      <c r="S9" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T9" s="53" t="str">
@@ -7364,7 +7516,7 @@
       <c r="R10" s="55" t="s">
         <v>571</v>
       </c>
-      <c r="S10" s="80" t="s">
+      <c r="S10" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T10" s="53" t="str">
@@ -7464,7 +7616,7 @@
       <c r="R11" s="55" t="s">
         <v>574</v>
       </c>
-      <c r="S11" s="80" t="s">
+      <c r="S11" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T11" s="53" t="str">
@@ -7564,7 +7716,7 @@
       <c r="R12" s="55" t="s">
         <v>577</v>
       </c>
-      <c r="S12" s="80" t="s">
+      <c r="S12" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T12" s="53" t="str">
@@ -7664,7 +7816,7 @@
       <c r="R13" s="55" t="s">
         <v>580</v>
       </c>
-      <c r="S13" s="80" t="s">
+      <c r="S13" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T13" s="53" t="str">
@@ -7764,7 +7916,7 @@
       <c r="R14" s="55" t="s">
         <v>583</v>
       </c>
-      <c r="S14" s="80" t="s">
+      <c r="S14" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T14" s="53" t="str">
@@ -7840,7 +7992,7 @@
         <v>196</v>
       </c>
       <c r="L15" s="52" t="str">
-        <f t="shared" ref="L15:M30" si="4">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:L27" si="4">CONCATENATE("", C15)</f>
         <v>Normativos</v>
       </c>
       <c r="M15" s="52" t="str">
@@ -7864,7 +8016,7 @@
       <c r="R15" s="38" t="s">
         <v>624</v>
       </c>
-      <c r="S15" s="80" t="s">
+      <c r="S15" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T15" s="53" t="str">
@@ -7964,7 +8116,7 @@
       <c r="R16" s="38" t="s">
         <v>625</v>
       </c>
-      <c r="S16" s="80" t="s">
+      <c r="S16" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T16" s="53" t="str">
@@ -8064,7 +8216,7 @@
       <c r="R17" s="38" t="s">
         <v>626</v>
       </c>
-      <c r="S17" s="80" t="s">
+      <c r="S17" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T17" s="53" t="str">
@@ -8164,7 +8316,7 @@
       <c r="R18" s="38" t="s">
         <v>627</v>
       </c>
-      <c r="S18" s="80" t="s">
+      <c r="S18" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T18" s="53" t="str">
@@ -8264,7 +8416,7 @@
       <c r="R19" s="38" t="s">
         <v>628</v>
       </c>
-      <c r="S19" s="80" t="s">
+      <c r="S19" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T19" s="53" t="str">
@@ -8364,7 +8516,7 @@
       <c r="R20" s="38" t="s">
         <v>629</v>
       </c>
-      <c r="S20" s="80" t="s">
+      <c r="S20" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T20" s="53" t="str">
@@ -8464,7 +8616,7 @@
       <c r="R21" s="38" t="s">
         <v>630</v>
       </c>
-      <c r="S21" s="80" t="s">
+      <c r="S21" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T21" s="53" t="str">
@@ -8564,7 +8716,7 @@
       <c r="R22" s="38" t="s">
         <v>631</v>
       </c>
-      <c r="S22" s="80" t="s">
+      <c r="S22" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T22" s="53" t="str">
@@ -8664,7 +8816,7 @@
       <c r="R23" s="38" t="s">
         <v>632</v>
       </c>
-      <c r="S23" s="80" t="s">
+      <c r="S23" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T23" s="53" t="str">
@@ -8764,7 +8916,7 @@
       <c r="R24" s="38" t="s">
         <v>633</v>
       </c>
-      <c r="S24" s="80" t="s">
+      <c r="S24" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T24" s="53" t="str">
@@ -8864,7 +9016,7 @@
       <c r="R25" s="38" t="s">
         <v>634</v>
       </c>
-      <c r="S25" s="80" t="s">
+      <c r="S25" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T25" s="53" t="str">
@@ -8964,7 +9116,7 @@
       <c r="R26" s="38" t="s">
         <v>635</v>
       </c>
-      <c r="S26" s="80" t="s">
+      <c r="S26" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T26" s="53" t="str">
@@ -9064,7 +9216,7 @@
       <c r="R27" s="38" t="s">
         <v>636</v>
       </c>
-      <c r="S27" s="80" t="s">
+      <c r="S27" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T27" s="53" t="str">
@@ -9105,72 +9257,72 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50">
         <v>28</v>
       </c>
       <c r="B28" s="54" t="s">
+        <v>695</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="D28" s="30" t="s">
         <v>697</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="E28" s="30" t="s">
         <v>698</v>
       </c>
-      <c r="E28" s="30" t="s">
-        <v>699</v>
-      </c>
       <c r="F28" s="30" t="s">
+        <v>674</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J28" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="K28" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="L28" s="52" t="s">
+        <v>696</v>
+      </c>
+      <c r="M28" s="52" t="s">
+        <v>697</v>
+      </c>
+      <c r="N28" s="52" t="s">
+        <v>701</v>
+      </c>
+      <c r="O28" s="52" t="s">
+        <v>702</v>
+      </c>
+      <c r="P28" s="38" t="s">
         <v>675</v>
       </c>
-      <c r="G28" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H28" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="I28" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="J28" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="K28" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="L28" s="52" t="s">
-        <v>697</v>
-      </c>
-      <c r="M28" s="52" t="s">
-        <v>698</v>
-      </c>
-      <c r="N28" s="52" t="s">
-        <v>702</v>
-      </c>
-      <c r="O28" s="52" t="s">
+      <c r="Q28" s="38" t="s">
+        <v>676</v>
+      </c>
+      <c r="R28" s="38" t="s">
+        <v>677</v>
+      </c>
+      <c r="S28" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="T28" s="38" t="s">
         <v>703</v>
       </c>
-      <c r="P28" s="38" t="s">
-        <v>676</v>
-      </c>
-      <c r="Q28" s="38" t="s">
-        <v>677</v>
-      </c>
-      <c r="R28" s="38" t="s">
-        <v>678</v>
-      </c>
-      <c r="S28" s="80" t="s">
-        <v>196</v>
-      </c>
-      <c r="T28" s="38" t="s">
+      <c r="U28" s="38" t="s">
         <v>704</v>
       </c>
-      <c r="U28" s="38" t="s">
-        <v>705</v>
-      </c>
       <c r="V28" s="53" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W28" s="38" t="s">
         <v>471</v>
@@ -9198,72 +9350,72 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="50">
         <v>29</v>
       </c>
       <c r="B29" s="54" t="s">
+        <v>695</v>
+      </c>
+      <c r="C29" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="D29" s="30" t="s">
         <v>697</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="E29" s="30" t="s">
         <v>698</v>
       </c>
-      <c r="E29" s="30" t="s">
-        <v>699</v>
-      </c>
       <c r="F29" s="30" t="s">
+        <v>678</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="K29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="L29" s="52" t="s">
+        <v>696</v>
+      </c>
+      <c r="M29" s="52" t="s">
+        <v>697</v>
+      </c>
+      <c r="N29" s="52" t="s">
+        <v>701</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>705</v>
+      </c>
+      <c r="P29" s="38" t="s">
         <v>679</v>
       </c>
-      <c r="G29" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="J29" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="K29" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="L29" s="52" t="s">
-        <v>697</v>
-      </c>
-      <c r="M29" s="52" t="s">
-        <v>698</v>
-      </c>
-      <c r="N29" s="52" t="s">
-        <v>702</v>
-      </c>
-      <c r="O29" s="52" t="s">
-        <v>706</v>
-      </c>
-      <c r="P29" s="38" t="s">
+      <c r="Q29" s="38" t="s">
         <v>680</v>
       </c>
-      <c r="Q29" s="38" t="s">
+      <c r="R29" s="38" t="s">
         <v>681</v>
       </c>
-      <c r="R29" s="38" t="s">
-        <v>682</v>
-      </c>
-      <c r="S29" s="80" t="s">
+      <c r="S29" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T29" s="38" t="s">
+        <v>703</v>
+      </c>
+      <c r="U29" s="38" t="s">
         <v>704</v>
       </c>
-      <c r="U29" s="38" t="s">
-        <v>705</v>
-      </c>
       <c r="V29" s="53" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W29" s="38" t="s">
         <v>471</v>
@@ -9291,72 +9443,72 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="50">
         <v>30</v>
       </c>
       <c r="B30" s="54" t="s">
+        <v>695</v>
+      </c>
+      <c r="C30" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="D30" s="30" t="s">
         <v>697</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="E30" s="30" t="s">
         <v>698</v>
       </c>
-      <c r="E30" s="30" t="s">
-        <v>699</v>
-      </c>
       <c r="F30" s="30" t="s">
+        <v>682</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J30" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="L30" s="52" t="s">
+        <v>696</v>
+      </c>
+      <c r="M30" s="52" t="s">
+        <v>697</v>
+      </c>
+      <c r="N30" s="52" t="s">
+        <v>701</v>
+      </c>
+      <c r="O30" s="52" t="s">
+        <v>706</v>
+      </c>
+      <c r="P30" s="38" t="s">
         <v>683</v>
       </c>
-      <c r="G30" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H30" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="J30" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="K30" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="L30" s="52" t="s">
-        <v>697</v>
-      </c>
-      <c r="M30" s="52" t="s">
-        <v>698</v>
-      </c>
-      <c r="N30" s="52" t="s">
-        <v>702</v>
-      </c>
-      <c r="O30" s="52" t="s">
-        <v>707</v>
-      </c>
-      <c r="P30" s="38" t="s">
+      <c r="Q30" s="38" t="s">
         <v>684</v>
       </c>
-      <c r="Q30" s="38" t="s">
+      <c r="R30" s="38" t="s">
         <v>685</v>
       </c>
-      <c r="R30" s="38" t="s">
-        <v>686</v>
-      </c>
-      <c r="S30" s="80" t="s">
+      <c r="S30" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T30" s="38" t="s">
+        <v>703</v>
+      </c>
+      <c r="U30" s="38" t="s">
         <v>704</v>
       </c>
-      <c r="U30" s="38" t="s">
-        <v>705</v>
-      </c>
       <c r="V30" s="53" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W30" s="38" t="s">
         <v>471</v>
@@ -9384,72 +9536,72 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50">
         <v>31</v>
       </c>
       <c r="B31" s="54" t="s">
+        <v>695</v>
+      </c>
+      <c r="C31" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="D31" s="30" t="s">
         <v>697</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="E31" s="30" t="s">
         <v>698</v>
       </c>
-      <c r="E31" s="30" t="s">
-        <v>699</v>
-      </c>
       <c r="F31" s="30" t="s">
+        <v>686</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J31" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="L31" s="52" t="s">
+        <v>696</v>
+      </c>
+      <c r="M31" s="52" t="s">
+        <v>697</v>
+      </c>
+      <c r="N31" s="52" t="s">
+        <v>701</v>
+      </c>
+      <c r="O31" s="52" t="s">
+        <v>707</v>
+      </c>
+      <c r="P31" s="38" t="s">
         <v>687</v>
       </c>
-      <c r="G31" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H31" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="J31" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="K31" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="L31" s="52" t="s">
-        <v>697</v>
-      </c>
-      <c r="M31" s="52" t="s">
-        <v>698</v>
-      </c>
-      <c r="N31" s="52" t="s">
-        <v>702</v>
-      </c>
-      <c r="O31" s="52" t="s">
-        <v>708</v>
-      </c>
-      <c r="P31" s="38" t="s">
+      <c r="Q31" s="38" t="s">
         <v>688</v>
       </c>
-      <c r="Q31" s="38" t="s">
+      <c r="R31" s="38" t="s">
         <v>689</v>
       </c>
-      <c r="R31" s="38" t="s">
-        <v>690</v>
-      </c>
-      <c r="S31" s="80" t="s">
+      <c r="S31" s="79" t="s">
         <v>196</v>
       </c>
       <c r="T31" s="38" t="s">
+        <v>703</v>
+      </c>
+      <c r="U31" s="38" t="s">
         <v>704</v>
       </c>
-      <c r="U31" s="38" t="s">
-        <v>705</v>
-      </c>
       <c r="V31" s="53" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W31" s="38" t="s">
         <v>471</v>
@@ -9477,72 +9629,72 @@
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:30" s="81" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="50">
         <v>32</v>
       </c>
       <c r="B32" s="54" t="s">
+        <v>695</v>
+      </c>
+      <c r="C32" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="C32" s="30" t="s">
-        <v>697</v>
-      </c>
       <c r="D32" s="30" t="s">
+        <v>699</v>
+      </c>
+      <c r="E32" s="30" t="s">
         <v>700</v>
       </c>
-      <c r="E32" s="30" t="s">
-        <v>701</v>
-      </c>
       <c r="F32" s="30" t="s">
+        <v>690</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="L32" s="52" t="s">
+        <v>696</v>
+      </c>
+      <c r="M32" s="52" t="s">
+        <v>699</v>
+      </c>
+      <c r="N32" s="52" t="s">
+        <v>708</v>
+      </c>
+      <c r="O32" s="52" t="s">
+        <v>709</v>
+      </c>
+      <c r="P32" s="38" t="s">
         <v>691</v>
       </c>
-      <c r="G32" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H32" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="I32" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="J32" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="L32" s="52" t="s">
-        <v>697</v>
-      </c>
-      <c r="M32" s="52" t="s">
-        <v>700</v>
-      </c>
-      <c r="N32" s="52" t="s">
-        <v>709</v>
-      </c>
-      <c r="O32" s="52" t="s">
+      <c r="Q32" s="38" t="s">
+        <v>692</v>
+      </c>
+      <c r="R32" s="38" t="s">
+        <v>693</v>
+      </c>
+      <c r="S32" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="T32" s="38" t="s">
+        <v>703</v>
+      </c>
+      <c r="U32" s="38" t="s">
         <v>710</v>
       </c>
-      <c r="P32" s="38" t="s">
-        <v>692</v>
-      </c>
-      <c r="Q32" s="38" t="s">
-        <v>693</v>
-      </c>
-      <c r="R32" s="38" t="s">
-        <v>694</v>
-      </c>
-      <c r="S32" s="80" t="s">
-        <v>196</v>
-      </c>
-      <c r="T32" s="38" t="s">
-        <v>704</v>
-      </c>
-      <c r="U32" s="38" t="s">
-        <v>711</v>
-      </c>
       <c r="V32" s="53" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="W32" s="38" t="s">
         <v>471</v>
@@ -9572,34 +9724,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B27 A28:A32">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="37" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="36" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F32">
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R27">
-    <cfRule type="cellIs" dxfId="31" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="30" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F32">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F32">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -9750,7 +9900,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9795,7 +9945,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10218,34 +10368,34 @@
         <v>196</v>
       </c>
       <c r="X4" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y4" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z4" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA4" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB4" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC4" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD4" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE4" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF4" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG4" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10319,34 +10469,34 @@
         <v>196</v>
       </c>
       <c r="X5" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y5" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z5" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA5" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB5" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC5" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD5" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE5" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF5" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG5" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10420,34 +10570,34 @@
         <v>196</v>
       </c>
       <c r="X6" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y6" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z6" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA6" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB6" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC6" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD6" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE6" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF6" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG6" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10521,34 +10671,34 @@
         <v>196</v>
       </c>
       <c r="X7" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y7" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z7" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA7" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB7" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC7" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD7" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE7" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF7" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG7" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10622,34 +10772,34 @@
         <v>196</v>
       </c>
       <c r="X8" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y8" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z8" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA8" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB8" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC8" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD8" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE8" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF8" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG8" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10723,34 +10873,34 @@
         <v>196</v>
       </c>
       <c r="X9" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y9" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z9" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA9" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB9" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC9" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD9" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE9" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF9" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG9" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10824,34 +10974,34 @@
         <v>196</v>
       </c>
       <c r="X10" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y10" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z10" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA10" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB10" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC10" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD10" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE10" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF10" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG10" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10925,34 +11075,34 @@
         <v>196</v>
       </c>
       <c r="X11" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y11" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z11" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA11" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB11" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC11" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD11" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE11" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF11" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG11" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11026,34 +11176,34 @@
         <v>196</v>
       </c>
       <c r="X12" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y12" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z12" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA12" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB12" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC12" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD12" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE12" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF12" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG12" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11127,34 +11277,34 @@
         <v>196</v>
       </c>
       <c r="X13" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y13" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z13" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA13" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB13" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC13" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD13" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE13" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF13" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG13" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11228,34 +11378,34 @@
         <v>196</v>
       </c>
       <c r="X14" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y14" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z14" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA14" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB14" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC14" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD14" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE14" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF14" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG14" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11329,34 +11479,34 @@
         <v>196</v>
       </c>
       <c r="X15" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y15" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z15" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA15" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB15" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC15" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD15" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE15" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF15" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG15" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11430,34 +11580,34 @@
         <v>196</v>
       </c>
       <c r="X16" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y16" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z16" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA16" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB16" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC16" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD16" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE16" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF16" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG16" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11531,34 +11681,34 @@
         <v>196</v>
       </c>
       <c r="X17" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y17" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z17" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA17" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB17" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC17" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD17" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE17" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF17" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG17" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11632,34 +11782,34 @@
         <v>196</v>
       </c>
       <c r="X18" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y18" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z18" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA18" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB18" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC18" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD18" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE18" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF18" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG18" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11733,34 +11883,34 @@
         <v>196</v>
       </c>
       <c r="X19" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y19" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z19" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA19" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB19" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC19" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD19" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE19" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF19" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG19" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11834,34 +11984,34 @@
         <v>196</v>
       </c>
       <c r="X20" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y20" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z20" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA20" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB20" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC20" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD20" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE20" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF20" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG20" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11935,34 +12085,34 @@
         <v>196</v>
       </c>
       <c r="X21" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y21" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z21" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA21" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB21" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC21" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD21" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE21" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF21" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG21" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12036,34 +12186,34 @@
         <v>196</v>
       </c>
       <c r="X22" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y22" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z22" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA22" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB22" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC22" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD22" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE22" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF22" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG22" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12137,34 +12287,34 @@
         <v>196</v>
       </c>
       <c r="X23" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y23" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z23" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA23" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB23" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC23" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD23" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE23" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF23" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG23" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="24" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12238,34 +12388,34 @@
         <v>196</v>
       </c>
       <c r="X24" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y24" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z24" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA24" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB24" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC24" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD24" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE24" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF24" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG24" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12339,34 +12489,34 @@
         <v>196</v>
       </c>
       <c r="X25" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y25" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z25" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA25" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB25" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC25" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD25" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE25" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF25" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG25" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12440,34 +12590,34 @@
         <v>196</v>
       </c>
       <c r="X26" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y26" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z26" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA26" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB26" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC26" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD26" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE26" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF26" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG26" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12541,34 +12691,34 @@
         <v>196</v>
       </c>
       <c r="X27" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y27" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z27" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA27" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB27" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC27" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD27" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE27" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF27" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG27" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12642,34 +12792,34 @@
         <v>196</v>
       </c>
       <c r="X28" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y28" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z28" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA28" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB28" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC28" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD28" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE28" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF28" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG28" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="29" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12743,34 +12893,34 @@
         <v>196</v>
       </c>
       <c r="X29" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y29" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z29" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA29" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB29" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC29" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD29" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE29" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF29" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG29" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12844,34 +12994,34 @@
         <v>196</v>
       </c>
       <c r="X30" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y30" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z30" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA30" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB30" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC30" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD30" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE30" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF30" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG30" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12945,34 +13095,34 @@
         <v>196</v>
       </c>
       <c r="X31" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y31" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z31" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA31" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB31" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC31" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD31" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE31" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF31" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG31" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13046,34 +13196,34 @@
         <v>196</v>
       </c>
       <c r="X32" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y32" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z32" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA32" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB32" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC32" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD32" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE32" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF32" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG32" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="33" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13147,34 +13297,34 @@
         <v>196</v>
       </c>
       <c r="X33" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y33" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z33" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA33" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB33" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC33" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD33" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE33" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF33" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG33" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="34" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13248,34 +13398,34 @@
         <v>196</v>
       </c>
       <c r="X34" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y34" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z34" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA34" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB34" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC34" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD34" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE34" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF34" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG34" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="35" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13349,34 +13499,34 @@
         <v>196</v>
       </c>
       <c r="X35" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y35" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z35" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA35" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB35" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC35" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD35" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE35" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF35" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG35" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="36" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13450,34 +13600,34 @@
         <v>196</v>
       </c>
       <c r="X36" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y36" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z36" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA36" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB36" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC36" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD36" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE36" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF36" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG36" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="37" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13551,34 +13701,34 @@
         <v>196</v>
       </c>
       <c r="X37" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y37" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z37" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA37" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB37" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC37" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD37" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE37" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF37" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG37" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="38" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13652,34 +13802,34 @@
         <v>196</v>
       </c>
       <c r="X38" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y38" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z38" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA38" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB38" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC38" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD38" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE38" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF38" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG38" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="39" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13753,34 +13903,34 @@
         <v>196</v>
       </c>
       <c r="X39" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y39" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z39" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA39" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB39" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC39" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD39" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE39" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF39" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG39" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="40" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13854,34 +14004,34 @@
         <v>196</v>
       </c>
       <c r="X40" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y40" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z40" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA40" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB40" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC40" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD40" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE40" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF40" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG40" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="41" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13955,34 +14105,34 @@
         <v>196</v>
       </c>
       <c r="X41" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y41" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z41" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA41" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB41" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC41" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD41" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE41" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF41" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG41" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="42" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14056,34 +14206,34 @@
         <v>196</v>
       </c>
       <c r="X42" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y42" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z42" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA42" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB42" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC42" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD42" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE42" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF42" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG42" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="43" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14157,34 +14307,34 @@
         <v>196</v>
       </c>
       <c r="X43" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y43" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z43" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA43" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB43" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC43" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD43" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE43" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF43" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG43" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="44" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14258,34 +14408,34 @@
         <v>196</v>
       </c>
       <c r="X44" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y44" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z44" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA44" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB44" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC44" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD44" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE44" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF44" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG44" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="45" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14359,34 +14509,34 @@
         <v>196</v>
       </c>
       <c r="X45" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y45" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z45" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA45" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB45" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC45" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD45" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE45" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF45" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG45" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="46" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14460,34 +14610,34 @@
         <v>196</v>
       </c>
       <c r="X46" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y46" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z46" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA46" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB46" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC46" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD46" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE46" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF46" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG46" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="47" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14561,34 +14711,34 @@
         <v>196</v>
       </c>
       <c r="X47" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y47" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z47" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA47" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB47" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC47" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD47" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE47" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF47" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG47" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="48" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14662,34 +14812,34 @@
         <v>196</v>
       </c>
       <c r="X48" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y48" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z48" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA48" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB48" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC48" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD48" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE48" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF48" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG48" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="49" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14763,34 +14913,34 @@
         <v>196</v>
       </c>
       <c r="X49" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y49" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z49" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA49" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB49" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC49" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD49" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE49" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF49" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG49" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="50" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14864,34 +15014,34 @@
         <v>196</v>
       </c>
       <c r="X50" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y50" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z50" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA50" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB50" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC50" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD50" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE50" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF50" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG50" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="51" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14965,34 +15115,34 @@
         <v>196</v>
       </c>
       <c r="X51" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y51" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z51" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA51" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB51" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC51" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD51" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE51" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF51" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG51" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="52" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15066,34 +15216,34 @@
         <v>196</v>
       </c>
       <c r="X52" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y52" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z52" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA52" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB52" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC52" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD52" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE52" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF52" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG52" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="53" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15167,34 +15317,34 @@
         <v>196</v>
       </c>
       <c r="X53" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y53" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z53" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA53" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB53" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC53" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD53" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE53" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF53" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG53" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="54" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15268,34 +15418,34 @@
         <v>196</v>
       </c>
       <c r="X54" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y54" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z54" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA54" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB54" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC54" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD54" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE54" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF54" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG54" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="55" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15369,34 +15519,34 @@
         <v>196</v>
       </c>
       <c r="X55" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y55" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z55" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA55" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB55" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC55" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD55" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE55" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF55" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG55" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="56" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15470,34 +15620,34 @@
         <v>196</v>
       </c>
       <c r="X56" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y56" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z56" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA56" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB56" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC56" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD56" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE56" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF56" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG56" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="57" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15571,34 +15721,34 @@
         <v>196</v>
       </c>
       <c r="X57" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y57" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z57" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA57" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB57" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC57" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD57" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE57" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF57" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG57" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="58" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15672,34 +15822,34 @@
         <v>196</v>
       </c>
       <c r="X58" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y58" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z58" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA58" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB58" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC58" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD58" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE58" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF58" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG58" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="59" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15773,34 +15923,34 @@
         <v>196</v>
       </c>
       <c r="X59" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y59" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z59" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA59" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB59" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC59" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD59" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE59" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF59" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG59" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="60" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15874,34 +16024,34 @@
         <v>196</v>
       </c>
       <c r="X60" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y60" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z60" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA60" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB60" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC60" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD60" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE60" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF60" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG60" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="61" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15975,34 +16125,34 @@
         <v>196</v>
       </c>
       <c r="X61" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y61" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z61" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA61" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB61" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC61" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD61" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE61" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF61" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG61" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="62" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16076,34 +16226,34 @@
         <v>196</v>
       </c>
       <c r="X62" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y62" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z62" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA62" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB62" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC62" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD62" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE62" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF62" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG62" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="63" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16177,34 +16327,34 @@
         <v>196</v>
       </c>
       <c r="X63" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y63" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z63" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA63" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB63" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC63" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD63" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE63" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF63" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG63" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16278,34 +16428,34 @@
         <v>196</v>
       </c>
       <c r="X64" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y64" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z64" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA64" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB64" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC64" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD64" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE64" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF64" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG64" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="65" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16379,34 +16529,34 @@
         <v>196</v>
       </c>
       <c r="X65" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y65" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z65" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA65" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB65" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC65" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD65" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE65" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF65" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG65" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="66" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16480,34 +16630,34 @@
         <v>196</v>
       </c>
       <c r="X66" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y66" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z66" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA66" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB66" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC66" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD66" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE66" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF66" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG66" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="67" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16581,34 +16731,34 @@
         <v>196</v>
       </c>
       <c r="X67" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y67" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z67" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA67" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB67" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC67" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD67" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE67" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF67" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG67" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="68" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16682,34 +16832,34 @@
         <v>196</v>
       </c>
       <c r="X68" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y68" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z68" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA68" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB68" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC68" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD68" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE68" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF68" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG68" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="69" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16783,34 +16933,34 @@
         <v>196</v>
       </c>
       <c r="X69" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y69" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z69" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA69" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB69" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC69" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD69" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE69" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF69" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG69" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="70" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16884,34 +17034,34 @@
         <v>196</v>
       </c>
       <c r="X70" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y70" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z70" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA70" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB70" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC70" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD70" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE70" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF70" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG70" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="71" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16985,34 +17135,34 @@
         <v>196</v>
       </c>
       <c r="X71" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y71" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z71" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA71" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB71" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC71" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD71" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE71" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF71" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG71" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="72" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17086,34 +17236,34 @@
         <v>196</v>
       </c>
       <c r="X72" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y72" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z72" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA72" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB72" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC72" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD72" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE72" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF72" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG72" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="73" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17187,34 +17337,34 @@
         <v>196</v>
       </c>
       <c r="X73" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y73" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z73" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA73" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB73" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC73" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD73" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE73" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF73" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG73" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="74" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17288,34 +17438,34 @@
         <v>196</v>
       </c>
       <c r="X74" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y74" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z74" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA74" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB74" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC74" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD74" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE74" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF74" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG74" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="75" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17389,34 +17539,34 @@
         <v>196</v>
       </c>
       <c r="X75" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y75" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z75" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA75" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB75" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC75" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD75" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE75" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF75" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG75" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="76" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17490,34 +17640,34 @@
         <v>196</v>
       </c>
       <c r="X76" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y76" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z76" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA76" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB76" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC76" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD76" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE76" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF76" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG76" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="77" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17591,34 +17741,34 @@
         <v>196</v>
       </c>
       <c r="X77" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y77" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z77" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA77" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB77" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC77" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD77" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE77" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF77" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG77" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="78" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17692,34 +17842,34 @@
         <v>196</v>
       </c>
       <c r="X78" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y78" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z78" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA78" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB78" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC78" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD78" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE78" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF78" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG78" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="79" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17793,34 +17943,34 @@
         <v>196</v>
       </c>
       <c r="X79" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y79" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z79" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA79" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB79" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC79" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD79" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE79" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF79" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG79" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="80" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17894,34 +18044,34 @@
         <v>196</v>
       </c>
       <c r="X80" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y80" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z80" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA80" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB80" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC80" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD80" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE80" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF80" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG80" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="81" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17995,34 +18145,34 @@
         <v>196</v>
       </c>
       <c r="X81" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y81" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z81" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA81" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB81" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC81" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD81" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE81" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF81" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG81" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="82" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18096,34 +18246,34 @@
         <v>196</v>
       </c>
       <c r="X82" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y82" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z82" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA82" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB82" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC82" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD82" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE82" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF82" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG82" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="83" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18197,34 +18347,34 @@
         <v>196</v>
       </c>
       <c r="X83" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y83" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z83" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA83" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB83" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC83" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD83" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE83" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF83" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG83" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="84" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18298,34 +18448,34 @@
         <v>196</v>
       </c>
       <c r="X84" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y84" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z84" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA84" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB84" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC84" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD84" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE84" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF84" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG84" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="85" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18399,34 +18549,34 @@
         <v>196</v>
       </c>
       <c r="X85" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y85" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z85" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA85" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB85" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC85" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD85" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE85" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF85" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG85" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="86" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18500,34 +18650,34 @@
         <v>196</v>
       </c>
       <c r="X86" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y86" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z86" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA86" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB86" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC86" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD86" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE86" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF86" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG86" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="87" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18601,34 +18751,34 @@
         <v>196</v>
       </c>
       <c r="X87" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y87" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z87" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA87" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB87" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC87" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD87" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE87" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF87" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG87" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="88" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18702,34 +18852,34 @@
         <v>196</v>
       </c>
       <c r="X88" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y88" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z88" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA88" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB88" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC88" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD88" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE88" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF88" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG88" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="89" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18803,34 +18953,34 @@
         <v>196</v>
       </c>
       <c r="X89" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y89" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z89" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA89" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB89" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC89" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD89" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE89" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF89" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG89" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="90" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18904,34 +19054,34 @@
         <v>196</v>
       </c>
       <c r="X90" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y90" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z90" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA90" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB90" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC90" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD90" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE90" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF90" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG90" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="91" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19005,34 +19155,34 @@
         <v>196</v>
       </c>
       <c r="X91" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y91" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z91" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA91" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB91" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC91" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD91" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE91" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF91" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG91" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="92" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19106,34 +19256,34 @@
         <v>196</v>
       </c>
       <c r="X92" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y92" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z92" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA92" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB92" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC92" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD92" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE92" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF92" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG92" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="93" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19207,34 +19357,34 @@
         <v>196</v>
       </c>
       <c r="X93" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y93" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z93" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA93" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB93" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC93" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD93" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE93" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF93" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG93" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="94" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19308,34 +19458,34 @@
         <v>196</v>
       </c>
       <c r="X94" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y94" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z94" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA94" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB94" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC94" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD94" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE94" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF94" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG94" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="95" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19409,34 +19559,34 @@
         <v>196</v>
       </c>
       <c r="X95" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y95" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z95" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA95" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB95" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC95" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD95" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE95" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF95" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG95" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="96" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19510,34 +19660,34 @@
         <v>196</v>
       </c>
       <c r="X96" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y96" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z96" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA96" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB96" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC96" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD96" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE96" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF96" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG96" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="97" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19611,34 +19761,34 @@
         <v>196</v>
       </c>
       <c r="X97" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y97" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z97" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA97" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB97" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC97" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD97" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE97" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF97" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG97" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="98" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19712,34 +19862,34 @@
         <v>196</v>
       </c>
       <c r="X98" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y98" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z98" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA98" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB98" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC98" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD98" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE98" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF98" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG98" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="99" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19813,34 +19963,34 @@
         <v>196</v>
       </c>
       <c r="X99" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y99" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z99" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA99" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB99" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC99" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD99" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE99" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF99" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG99" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="100" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19914,34 +20064,34 @@
         <v>196</v>
       </c>
       <c r="X100" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y100" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z100" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA100" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB100" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC100" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD100" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE100" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF100" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG100" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="101" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20015,34 +20165,34 @@
         <v>196</v>
       </c>
       <c r="X101" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y101" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z101" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA101" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB101" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC101" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD101" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE101" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF101" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG101" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="102" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20116,34 +20266,34 @@
         <v>196</v>
       </c>
       <c r="X102" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y102" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z102" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA102" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB102" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC102" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD102" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE102" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF102" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG102" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="103" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20217,34 +20367,34 @@
         <v>196</v>
       </c>
       <c r="X103" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y103" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z103" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA103" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB103" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC103" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD103" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE103" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF103" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG103" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="104" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20318,34 +20468,34 @@
         <v>196</v>
       </c>
       <c r="X104" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y104" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z104" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA104" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB104" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC104" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD104" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE104" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF104" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG104" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="105" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20419,34 +20569,34 @@
         <v>196</v>
       </c>
       <c r="X105" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y105" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z105" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA105" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB105" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC105" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD105" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE105" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF105" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG105" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="106" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20520,34 +20670,34 @@
         <v>196</v>
       </c>
       <c r="X106" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y106" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z106" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA106" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB106" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC106" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD106" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE106" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF106" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG106" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="107" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20621,34 +20771,34 @@
         <v>196</v>
       </c>
       <c r="X107" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y107" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z107" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA107" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB107" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC107" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD107" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE107" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF107" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG107" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="108" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20722,34 +20872,34 @@
         <v>196</v>
       </c>
       <c r="X108" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y108" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z108" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA108" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB108" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC108" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD108" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE108" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF108" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG108" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="109" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20823,34 +20973,34 @@
         <v>196</v>
       </c>
       <c r="X109" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y109" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z109" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA109" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB109" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC109" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD109" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE109" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF109" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG109" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="110" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20924,34 +21074,34 @@
         <v>196</v>
       </c>
       <c r="X110" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y110" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z110" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA110" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB110" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC110" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD110" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE110" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF110" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG110" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="111" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21025,34 +21175,34 @@
         <v>196</v>
       </c>
       <c r="X111" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y111" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z111" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA111" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB111" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC111" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD111" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE111" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF111" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG111" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="112" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21126,34 +21276,34 @@
         <v>196</v>
       </c>
       <c r="X112" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y112" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z112" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA112" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB112" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC112" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD112" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE112" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF112" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG112" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="113" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21227,34 +21377,34 @@
         <v>196</v>
       </c>
       <c r="X113" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y113" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z113" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA113" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB113" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC113" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD113" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE113" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF113" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG113" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="114" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21328,34 +21478,34 @@
         <v>196</v>
       </c>
       <c r="X114" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y114" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z114" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA114" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB114" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC114" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD114" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE114" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF114" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG114" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="115" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21429,34 +21579,34 @@
         <v>196</v>
       </c>
       <c r="X115" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y115" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z115" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA115" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB115" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC115" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD115" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE115" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF115" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG115" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="116" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21530,34 +21680,34 @@
         <v>196</v>
       </c>
       <c r="X116" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y116" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z116" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA116" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB116" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC116" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD116" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE116" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF116" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG116" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="117" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21631,34 +21781,34 @@
         <v>196</v>
       </c>
       <c r="X117" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y117" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z117" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA117" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB117" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC117" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD117" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE117" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF117" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG117" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="118" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21732,34 +21882,34 @@
         <v>196</v>
       </c>
       <c r="X118" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y118" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z118" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA118" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB118" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC118" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD118" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE118" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF118" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG118" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="119" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21833,34 +21983,34 @@
         <v>196</v>
       </c>
       <c r="X119" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y119" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z119" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA119" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB119" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC119" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD119" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE119" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF119" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG119" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="120" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21934,34 +22084,34 @@
         <v>196</v>
       </c>
       <c r="X120" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y120" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z120" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA120" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB120" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC120" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD120" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE120" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF120" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG120" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="121" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22035,34 +22185,34 @@
         <v>196</v>
       </c>
       <c r="X121" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y121" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z121" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA121" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB121" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC121" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD121" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE121" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF121" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG121" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="122" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22136,34 +22286,34 @@
         <v>196</v>
       </c>
       <c r="X122" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y122" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z122" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA122" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB122" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC122" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD122" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE122" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF122" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG122" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="123" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22237,34 +22387,34 @@
         <v>196</v>
       </c>
       <c r="X123" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y123" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z123" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA123" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB123" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC123" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD123" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE123" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF123" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG123" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="124" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22338,34 +22488,34 @@
         <v>196</v>
       </c>
       <c r="X124" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y124" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z124" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA124" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB124" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC124" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD124" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE124" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF124" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG124" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="125" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22439,34 +22589,34 @@
         <v>196</v>
       </c>
       <c r="X125" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y125" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z125" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA125" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB125" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC125" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD125" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE125" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF125" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG125" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="126" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22540,34 +22690,34 @@
         <v>196</v>
       </c>
       <c r="X126" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y126" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z126" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA126" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB126" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC126" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD126" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE126" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF126" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG126" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="127" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22641,34 +22791,34 @@
         <v>196</v>
       </c>
       <c r="X127" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y127" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z127" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA127" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB127" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC127" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD127" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE127" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF127" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG127" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="128" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22742,34 +22892,34 @@
         <v>196</v>
       </c>
       <c r="X128" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y128" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z128" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA128" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB128" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC128" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD128" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE128" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF128" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG128" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="129" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22843,34 +22993,34 @@
         <v>196</v>
       </c>
       <c r="X129" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y129" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z129" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA129" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB129" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC129" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD129" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE129" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF129" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG129" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="130" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22944,34 +23094,34 @@
         <v>196</v>
       </c>
       <c r="X130" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y130" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z130" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA130" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB130" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC130" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD130" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE130" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF130" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG130" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="131" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23045,34 +23195,34 @@
         <v>196</v>
       </c>
       <c r="X131" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y131" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z131" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA131" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB131" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC131" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD131" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE131" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF131" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG131" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="132" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23146,34 +23296,34 @@
         <v>196</v>
       </c>
       <c r="X132" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y132" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z132" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA132" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB132" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC132" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD132" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE132" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF132" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG132" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="133" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23247,34 +23397,34 @@
         <v>196</v>
       </c>
       <c r="X133" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y133" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z133" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA133" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB133" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC133" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD133" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE133" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF133" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG133" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="134" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23348,34 +23498,34 @@
         <v>196</v>
       </c>
       <c r="X134" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y134" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z134" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA134" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB134" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC134" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD134" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE134" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF134" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG134" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="135" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23449,34 +23599,34 @@
         <v>196</v>
       </c>
       <c r="X135" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y135" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z135" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA135" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB135" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC135" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD135" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE135" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF135" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG135" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="136" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23550,34 +23700,34 @@
         <v>196</v>
       </c>
       <c r="X136" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y136" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z136" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA136" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB136" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC136" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD136" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE136" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF136" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG136" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="137" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23651,34 +23801,34 @@
         <v>196</v>
       </c>
       <c r="X137" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y137" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z137" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA137" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB137" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC137" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD137" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE137" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF137" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG137" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="138" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23752,34 +23902,34 @@
         <v>196</v>
       </c>
       <c r="X138" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y138" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z138" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA138" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB138" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC138" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD138" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE138" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF138" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG138" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="139" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23853,34 +24003,34 @@
         <v>196</v>
       </c>
       <c r="X139" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y139" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z139" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA139" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB139" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC139" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD139" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE139" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF139" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG139" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="140" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23954,34 +24104,34 @@
         <v>196</v>
       </c>
       <c r="X140" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y140" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z140" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA140" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB140" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC140" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD140" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE140" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF140" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG140" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="141" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24055,34 +24205,34 @@
         <v>196</v>
       </c>
       <c r="X141" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y141" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z141" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA141" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB141" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC141" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD141" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE141" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF141" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG141" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="142" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24156,34 +24306,34 @@
         <v>196</v>
       </c>
       <c r="X142" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y142" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z142" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA142" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB142" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC142" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD142" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE142" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF142" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG142" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="143" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24257,34 +24407,34 @@
         <v>196</v>
       </c>
       <c r="X143" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y143" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z143" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA143" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB143" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC143" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD143" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE143" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF143" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG143" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="144" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24358,34 +24508,34 @@
         <v>196</v>
       </c>
       <c r="X144" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y144" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z144" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA144" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB144" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC144" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD144" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE144" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF144" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG144" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="145" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24459,34 +24609,34 @@
         <v>196</v>
       </c>
       <c r="X145" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y145" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z145" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA145" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB145" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC145" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD145" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE145" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF145" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG145" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="146" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24560,34 +24710,34 @@
         <v>196</v>
       </c>
       <c r="X146" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y146" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z146" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA146" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB146" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC146" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD146" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE146" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF146" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG146" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="147" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24661,34 +24811,34 @@
         <v>196</v>
       </c>
       <c r="X147" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y147" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z147" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA147" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB147" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC147" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD147" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE147" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF147" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG147" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="148" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24762,34 +24912,34 @@
         <v>196</v>
       </c>
       <c r="X148" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y148" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z148" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA148" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB148" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC148" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD148" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE148" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF148" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG148" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="149" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24863,34 +25013,34 @@
         <v>196</v>
       </c>
       <c r="X149" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y149" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z149" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA149" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB149" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC149" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD149" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE149" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF149" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG149" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="150" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24964,34 +25114,34 @@
         <v>196</v>
       </c>
       <c r="X150" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y150" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z150" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA150" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB150" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC150" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD150" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE150" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF150" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG150" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="151" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25065,34 +25215,34 @@
         <v>196</v>
       </c>
       <c r="X151" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y151" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z151" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA151" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB151" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC151" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD151" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE151" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF151" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG151" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="152" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25166,34 +25316,34 @@
         <v>196</v>
       </c>
       <c r="X152" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y152" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z152" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA152" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB152" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC152" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD152" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE152" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF152" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG152" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="153" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25267,34 +25417,34 @@
         <v>196</v>
       </c>
       <c r="X153" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y153" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z153" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA153" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB153" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC153" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD153" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE153" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF153" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG153" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="154" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25368,34 +25518,34 @@
         <v>196</v>
       </c>
       <c r="X154" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y154" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z154" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA154" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB154" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC154" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD154" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE154" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF154" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG154" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="155" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25469,34 +25619,34 @@
         <v>196</v>
       </c>
       <c r="X155" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y155" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z155" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA155" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB155" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC155" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD155" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE155" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF155" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG155" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="156" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25570,34 +25720,34 @@
         <v>196</v>
       </c>
       <c r="X156" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y156" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z156" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA156" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB156" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC156" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD156" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE156" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF156" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG156" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="157" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25671,34 +25821,34 @@
         <v>196</v>
       </c>
       <c r="X157" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y157" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z157" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA157" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB157" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC157" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD157" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE157" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF157" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG157" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="158" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25772,34 +25922,34 @@
         <v>196</v>
       </c>
       <c r="X158" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y158" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z158" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA158" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB158" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC158" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD158" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE158" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF158" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG158" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="159" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25873,34 +26023,34 @@
         <v>196</v>
       </c>
       <c r="X159" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y159" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z159" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA159" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB159" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC159" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD159" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE159" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF159" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG159" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="160" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -25974,34 +26124,34 @@
         <v>196</v>
       </c>
       <c r="X160" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y160" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z160" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA160" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB160" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC160" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD160" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE160" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF160" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG160" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="161" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26075,34 +26225,34 @@
         <v>196</v>
       </c>
       <c r="X161" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y161" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z161" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA161" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB161" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC161" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD161" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE161" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF161" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG161" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="162" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26176,34 +26326,34 @@
         <v>196</v>
       </c>
       <c r="X162" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y162" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z162" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA162" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB162" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC162" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD162" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE162" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF162" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG162" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="163" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26277,34 +26427,34 @@
         <v>196</v>
       </c>
       <c r="X163" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y163" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z163" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA163" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB163" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC163" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD163" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE163" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF163" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG163" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="164" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26378,34 +26528,34 @@
         <v>196</v>
       </c>
       <c r="X164" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y164" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z164" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA164" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB164" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC164" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD164" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE164" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF164" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG164" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="165" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26479,34 +26629,34 @@
         <v>196</v>
       </c>
       <c r="X165" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y165" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z165" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA165" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB165" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC165" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD165" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE165" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF165" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG165" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="166" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26580,34 +26730,34 @@
         <v>196</v>
       </c>
       <c r="X166" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y166" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z166" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA166" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB166" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC166" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD166" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE166" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF166" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG166" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="167" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26681,34 +26831,34 @@
         <v>196</v>
       </c>
       <c r="X167" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y167" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z167" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA167" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB167" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC167" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD167" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE167" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF167" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG167" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="168" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26782,34 +26932,34 @@
         <v>196</v>
       </c>
       <c r="X168" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y168" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z168" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA168" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB168" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC168" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD168" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE168" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF168" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG168" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="169" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26883,34 +27033,34 @@
         <v>196</v>
       </c>
       <c r="X169" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y169" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z169" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA169" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB169" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC169" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD169" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE169" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF169" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG169" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="170" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -26984,34 +27134,34 @@
         <v>196</v>
       </c>
       <c r="X170" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y170" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z170" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA170" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB170" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC170" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD170" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE170" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF170" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG170" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="171" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27085,34 +27235,34 @@
         <v>196</v>
       </c>
       <c r="X171" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y171" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z171" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA171" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB171" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC171" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD171" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE171" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF171" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG171" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="172" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27186,34 +27336,34 @@
         <v>196</v>
       </c>
       <c r="X172" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y172" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z172" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA172" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB172" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC172" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD172" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE172" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF172" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG172" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="173" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27287,34 +27437,34 @@
         <v>196</v>
       </c>
       <c r="X173" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y173" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z173" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA173" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB173" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC173" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD173" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE173" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF173" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG173" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="174" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27388,34 +27538,34 @@
         <v>196</v>
       </c>
       <c r="X174" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y174" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z174" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA174" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB174" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC174" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD174" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE174" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF174" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG174" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="175" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27489,34 +27639,34 @@
         <v>196</v>
       </c>
       <c r="X175" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y175" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z175" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA175" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB175" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC175" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD175" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE175" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF175" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG175" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="176" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27590,34 +27740,34 @@
         <v>196</v>
       </c>
       <c r="X176" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y176" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z176" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA176" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB176" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC176" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD176" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE176" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF176" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG176" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="177" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27691,34 +27841,34 @@
         <v>196</v>
       </c>
       <c r="X177" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y177" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z177" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA177" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB177" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC177" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD177" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE177" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF177" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG177" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="178" spans="1:33" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -27792,34 +27942,34 @@
         <v>196</v>
       </c>
       <c r="X178" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y178" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z178" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA178" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB178" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC178" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD178" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE178" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF178" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG178" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="179" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27827,10 +27977,10 @@
         <v>179</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="C179" s="10" t="s">
         <v>652</v>
+      </c>
+      <c r="C179" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="D179" s="34" t="s">
         <v>196</v>
@@ -27854,26 +28004,26 @@
         <v>376</v>
       </c>
       <c r="K179" s="35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L179" s="34" t="s">
         <v>432</v>
       </c>
       <c r="M179" s="35" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="N179" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O179" s="76" t="s">
-        <v>656</v>
-      </c>
-      <c r="P179" s="78" t="str">
+      <c r="O179" s="75" t="s">
+        <v>655</v>
+      </c>
+      <c r="P179" s="77" t="str">
         <f t="shared" ref="P179:P183" si="0">IF(Q179="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Q179" s="79" t="s">
-        <v>670</v>
+      <c r="Q179" s="78" t="s">
+        <v>669</v>
       </c>
       <c r="R179" s="45" t="s">
         <v>196</v>
@@ -27894,34 +28044,34 @@
         <v>196</v>
       </c>
       <c r="X179" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y179" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z179" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA179" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB179" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC179" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD179" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE179" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF179" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG179" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="180" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27929,10 +28079,10 @@
         <v>180</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="C180" s="10" t="s">
-        <v>652</v>
+        <v>656</v>
+      </c>
+      <c r="C180" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="D180" s="34" t="s">
         <v>196</v>
@@ -27956,26 +28106,26 @@
         <v>376</v>
       </c>
       <c r="K180" s="35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L180" s="34" t="s">
         <v>432</v>
       </c>
       <c r="M180" s="35" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N180" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O180" s="76" t="s">
-        <v>659</v>
-      </c>
-      <c r="P180" s="78" t="str">
+      <c r="O180" s="75" t="s">
+        <v>658</v>
+      </c>
+      <c r="P180" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q180" s="79" t="s">
-        <v>671</v>
+      <c r="Q180" s="78" t="s">
+        <v>670</v>
       </c>
       <c r="R180" s="45" t="s">
         <v>196</v>
@@ -27996,34 +28146,34 @@
         <v>196</v>
       </c>
       <c r="X180" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y180" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z180" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA180" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB180" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC180" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD180" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE180" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF180" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG180" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="181" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28031,10 +28181,10 @@
         <v>181</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>660</v>
-      </c>
-      <c r="C181" s="10" t="s">
-        <v>652</v>
+        <v>659</v>
+      </c>
+      <c r="C181" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="D181" s="34" t="s">
         <v>196</v>
@@ -28058,26 +28208,26 @@
         <v>376</v>
       </c>
       <c r="K181" s="35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L181" s="34" t="s">
         <v>432</v>
       </c>
       <c r="M181" s="35" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N181" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O181" s="76" t="s">
-        <v>662</v>
-      </c>
-      <c r="P181" s="78" t="str">
+      <c r="O181" s="75" t="s">
+        <v>661</v>
+      </c>
+      <c r="P181" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q181" s="79" t="s">
-        <v>672</v>
+      <c r="Q181" s="78" t="s">
+        <v>671</v>
       </c>
       <c r="R181" s="45" t="s">
         <v>196</v>
@@ -28098,34 +28248,34 @@
         <v>196</v>
       </c>
       <c r="X181" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y181" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z181" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA181" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB181" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC181" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD181" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE181" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF181" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG181" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="182" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28133,10 +28283,10 @@
         <v>182</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="C182" s="10" t="s">
-        <v>652</v>
+        <v>662</v>
+      </c>
+      <c r="C182" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="D182" s="34" t="s">
         <v>196</v>
@@ -28160,26 +28310,26 @@
         <v>376</v>
       </c>
       <c r="K182" s="35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L182" s="34" t="s">
         <v>432</v>
       </c>
       <c r="M182" s="35" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N182" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="O182" s="76" t="s">
-        <v>665</v>
-      </c>
-      <c r="P182" s="78" t="str">
+      <c r="O182" s="75" t="s">
+        <v>664</v>
+      </c>
+      <c r="P182" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q182" s="79" t="s">
-        <v>673</v>
+      <c r="Q182" s="78" t="s">
+        <v>672</v>
       </c>
       <c r="R182" s="45" t="s">
         <v>196</v>
@@ -28200,34 +28350,34 @@
         <v>196</v>
       </c>
       <c r="X182" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y182" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z182" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA182" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB182" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC182" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD182" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE182" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF182" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG182" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="183" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28235,199 +28385,199 @@
         <v>183</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>666</v>
-      </c>
-      <c r="C183" s="72" t="s">
-        <v>652</v>
+        <v>665</v>
+      </c>
+      <c r="C183" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="D183" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="E183" s="73" t="s">
+      <c r="E183" s="72" t="s">
         <v>196</v>
       </c>
       <c r="F183" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="G183" s="73" t="s">
+      <c r="G183" s="72" t="s">
         <v>196</v>
       </c>
       <c r="H183" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="I183" s="73" t="s">
+      <c r="I183" s="72" t="s">
         <v>196</v>
       </c>
       <c r="J183" s="36" t="s">
         <v>376</v>
       </c>
-      <c r="K183" s="73" t="s">
-        <v>654</v>
+      <c r="K183" s="72" t="s">
+        <v>653</v>
       </c>
       <c r="L183" s="36" t="s">
         <v>432</v>
       </c>
-      <c r="M183" s="73" t="s">
-        <v>667</v>
+      <c r="M183" s="72" t="s">
+        <v>666</v>
       </c>
       <c r="N183" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="O183" s="77" t="s">
-        <v>668</v>
-      </c>
-      <c r="P183" s="78" t="str">
+      <c r="O183" s="76" t="s">
+        <v>667</v>
+      </c>
+      <c r="P183" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q183" s="79" t="s">
-        <v>674</v>
-      </c>
-      <c r="R183" s="75" t="s">
-        <v>196</v>
-      </c>
-      <c r="S183" s="74" t="s">
-        <v>196</v>
-      </c>
-      <c r="T183" s="75" t="s">
-        <v>196</v>
-      </c>
-      <c r="U183" s="74" t="s">
-        <v>196</v>
-      </c>
-      <c r="V183" s="75" t="s">
-        <v>196</v>
-      </c>
-      <c r="W183" s="74" t="s">
+      <c r="Q183" s="78" t="s">
+        <v>673</v>
+      </c>
+      <c r="R183" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="S183" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="T183" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="U183" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="V183" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="W183" s="73" t="s">
         <v>196</v>
       </c>
       <c r="X183" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Y183" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="Z183" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA183" s="57" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB183" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AC183" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AD183" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AE183" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AF183" s="56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG183" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B178 B184:B1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B179:B183">
-    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="24" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R179:W183">
-    <cfRule type="cellIs" dxfId="22" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1 V1 X1 F1 H1 J1 N1 P1 R1">
-    <cfRule type="cellIs" dxfId="21" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AG1 T2:W178">
-    <cfRule type="cellIs" dxfId="20" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Y183">
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z183">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA183">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB183">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC183">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD183">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE183">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF183">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG183">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
